--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Reports\Camera Reports\Dashboard\Starkey\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Starkey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8FFBC70-90E2-4AFD-8832-B85D628EA77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D5661B7-6D7F-40A8-AF5D-8FD22568D14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1665" windowWidth="23280" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4152" uniqueCount="977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4738" uniqueCount="1097">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -2917,6 +2917,15 @@
     <t>03/12/26 13:33 EDT</t>
   </si>
   <si>
+    <t>03/13/26 11:00 EDT</t>
+  </si>
+  <si>
+    <t>Arrick Estrada</t>
+  </si>
+  <si>
+    <t>03/16/26 11:51 EDT</t>
+  </si>
+  <si>
     <t>03/13/26 12:04 EDT</t>
   </si>
   <si>
@@ -2951,6 +2960,357 @@
   </si>
   <si>
     <t>1.9mi SW of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/16/26 09:23 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 09:30 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 09:36 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 09:43 EDT</t>
+  </si>
+  <si>
+    <t>David Wilkinson</t>
+  </si>
+  <si>
+    <t>4.6mi N of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/16/26 10:38 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 10:42 EDT</t>
+  </si>
+  <si>
+    <t>3.4mi N of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/16/26 11:02 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 11:14 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 11:21 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi NE of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/16/26 11:38 EDT</t>
+  </si>
+  <si>
+    <t>3.8mi N of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/16/26 11:50 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 11:57 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 09:46 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 10:58 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 11:00 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 11:07 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 12:04 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 12:07 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 12:10 EDT</t>
+  </si>
+  <si>
+    <t>7.2mi NW of Amarillo TX</t>
+  </si>
+  <si>
+    <t>03/17/26 12:13 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 12:21 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 12:24 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 13:19 EDT</t>
+  </si>
+  <si>
+    <t>8.5mi NW of Amarillo TX</t>
+  </si>
+  <si>
+    <t>03/17/26 13:33 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 13:51 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 13:55 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 14:06 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 14:14 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 14:18 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 14:32 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 14:56 EDT</t>
+  </si>
+  <si>
+    <t>5.5mi NW of Amarillo TX</t>
+  </si>
+  <si>
+    <t>03/17/26 15:08 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 15:10 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 15:26 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 17:20 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 08:38 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 08:45 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 08:56 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 09:42 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 10:15 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 11:20 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 11:44 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 12:33 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 13:20 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 14:14 EDT</t>
+  </si>
+  <si>
+    <t>8.6mi NE of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/18/26 14:27 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 14:28 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 14:29 EDT</t>
+  </si>
+  <si>
+    <t>9mi NE of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/18/26 14:32 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 14:37 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 15:20 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 15:21 EDT</t>
+  </si>
+  <si>
+    <t>8.9mi NE of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/18/26 15:22 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 15:23 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 15:24 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 15:38 EDT</t>
+  </si>
+  <si>
+    <t>6.1mi NE of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/19/26 09:01 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 09:24 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 10:39 EDT</t>
+  </si>
+  <si>
+    <t>3mi NW of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/19/26 10:40 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 10:42 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 10:45 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 11:09 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 11:13 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 11:32 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 11:57 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 12:01 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 12:04 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi N of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/19/26 12:05 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 12:08 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 12:39 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 12:41 EDT</t>
+  </si>
+  <si>
+    <t>7.4mi SW of Amarillo TX</t>
+  </si>
+  <si>
+    <t>03/19/26 13:13 EDT</t>
+  </si>
+  <si>
+    <t>5.4mi N of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/20/26 07:27 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 14:26 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 09:26 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 09:42 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 09:54 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 10:16 EDT</t>
+  </si>
+  <si>
+    <t>3.8mi SE of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/20/26 10:18 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 10:22 EDT</t>
+  </si>
+  <si>
+    <t>4.6mi SE of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/20/26 10:31 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 10:43 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 11:03 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 11:26 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi S of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/20/26 11:35 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 11:38 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 11:45 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi S of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/20/26 12:06 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 12:52 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 14:09 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 14:27 EDT</t>
+  </si>
+  <si>
+    <t>5.1mi E of Canyon TX</t>
+  </si>
+  <si>
+    <t>03/20/26 14:40 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 14:55 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 15:01 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 16:28 EDT</t>
   </si>
 </sst>
 </file>
@@ -3312,7 +3672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M687"/>
+  <dimension ref="A1:M783"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -5414,19 +5774,19 @@
         <v>157</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D74" s="3">
-        <v>5034778294</v>
+        <v>5034778913</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
@@ -5443,19 +5803,19 @@
         <v>157</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D75" s="3">
-        <v>5034778913</v>
+        <v>5034778294</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
@@ -23109,33 +23469,37 @@
         <v>965</v>
       </c>
       <c r="B681" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C681" s="3" t="s">
-        <v>23</v>
-      </c>
+        <v>966</v>
+      </c>
+      <c r="C681" s="3"/>
       <c r="D681" s="3">
-        <v>5398455504</v>
+        <v>5397970814</v>
       </c>
       <c r="E681" s="3" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="F681" s="3" t="s">
-        <v>877</v>
-      </c>
-      <c r="G681" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="G681" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="H681" s="3"/>
       <c r="I681" s="3"/>
       <c r="J681" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K681" s="3"/>
-      <c r="L681" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="K681" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L681" s="3" t="s">
+        <v>967</v>
+      </c>
       <c r="M681" s="3"/>
     </row>
     <row r="682" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A682" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B682" s="3" t="s">
         <v>22</v>
@@ -23144,13 +23508,13 @@
         <v>23</v>
       </c>
       <c r="D682" s="3">
-        <v>5399576311</v>
+        <v>5398455504</v>
       </c>
       <c r="E682" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F682" s="3" t="s">
-        <v>967</v>
+        <v>877</v>
       </c>
       <c r="G682" s="3"/>
       <c r="H682" s="3"/>
@@ -23164,22 +23528,22 @@
     </row>
     <row r="683" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A683" s="3" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C683" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D683" s="3">
-        <v>5399745867</v>
+        <v>5399576311</v>
       </c>
       <c r="E683" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F683" s="3" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="G683" s="3"/>
       <c r="H683" s="3"/>
@@ -23193,19 +23557,19 @@
     </row>
     <row r="684" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A684" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C684" s="3" t="s">
-        <v>971</v>
+        <v>28</v>
       </c>
       <c r="D684" s="3">
-        <v>5399832246</v>
+        <v>5399745867</v>
       </c>
       <c r="E684" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F684" s="3" t="s">
         <v>972</v>
@@ -23225,19 +23589,19 @@
         <v>973</v>
       </c>
       <c r="B685" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C685" s="3" t="s">
-        <v>28</v>
+        <v>974</v>
       </c>
       <c r="D685" s="3">
-        <v>5400140206</v>
+        <v>5399832246</v>
       </c>
       <c r="E685" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F685" s="3" t="s">
-        <v>580</v>
+        <v>975</v>
       </c>
       <c r="G685" s="3"/>
       <c r="H685" s="3"/>
@@ -23251,22 +23615,22 @@
     </row>
     <row r="686" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A686" s="3" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B686" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C686" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D686" s="3">
-        <v>5400156269</v>
+        <v>5400140206</v>
       </c>
       <c r="E686" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F686" s="3" t="s">
-        <v>83</v>
+        <v>580</v>
       </c>
       <c r="G686" s="3"/>
       <c r="H686" s="3"/>
@@ -23280,22 +23644,22 @@
     </row>
     <row r="687" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A687" s="3" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B687" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C687" s="3" t="s">
-        <v>971</v>
+        <v>23</v>
       </c>
       <c r="D687" s="3">
-        <v>5400504948</v>
+        <v>5400156269</v>
       </c>
       <c r="E687" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F687" s="3" t="s">
-        <v>976</v>
+        <v>83</v>
       </c>
       <c r="G687" s="3"/>
       <c r="H687" s="3"/>
@@ -23307,6 +23671,2806 @@
       <c r="L687" s="3"/>
       <c r="M687" s="3"/>
     </row>
+    <row r="688" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A688" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="B688" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C688" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D688" s="3">
+        <v>5400504948</v>
+      </c>
+      <c r="E688" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="G688" s="3"/>
+      <c r="H688" s="3"/>
+      <c r="I688" s="3"/>
+      <c r="J688" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K688" s="3"/>
+      <c r="L688" s="3"/>
+      <c r="M688" s="3"/>
+    </row>
+    <row r="689" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A689" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="B689" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C689" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D689" s="3">
+        <v>5412473649</v>
+      </c>
+      <c r="E689" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="G689" s="3"/>
+      <c r="H689" s="3"/>
+      <c r="I689" s="3"/>
+      <c r="J689" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K689" s="3"/>
+      <c r="L689" s="3"/>
+      <c r="M689" s="3"/>
+    </row>
+    <row r="690" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A690" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="B690" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C690" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D690" s="3">
+        <v>5412510089</v>
+      </c>
+      <c r="E690" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G690" s="3"/>
+      <c r="H690" s="3"/>
+      <c r="I690" s="3"/>
+      <c r="J690" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K690" s="3"/>
+      <c r="L690" s="3"/>
+      <c r="M690" s="3"/>
+    </row>
+    <row r="691" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A691" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="B691" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C691" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D691" s="3">
+        <v>5412538316</v>
+      </c>
+      <c r="E691" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G691" s="3"/>
+      <c r="H691" s="3"/>
+      <c r="I691" s="3"/>
+      <c r="J691" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K691" s="3"/>
+      <c r="L691" s="3"/>
+      <c r="M691" s="3"/>
+    </row>
+    <row r="692" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A692" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="B692" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="C692" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D692" s="3">
+        <v>5412572167</v>
+      </c>
+      <c r="E692" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H692" s="3"/>
+      <c r="I692" s="3"/>
+      <c r="J692" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K692" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L692" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="M692" s="3"/>
+    </row>
+    <row r="693" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A693" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="B693" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C693" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D693" s="3">
+        <v>5412864708</v>
+      </c>
+      <c r="E693" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G693" s="3"/>
+      <c r="H693" s="3"/>
+      <c r="I693" s="3"/>
+      <c r="J693" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K693" s="3"/>
+      <c r="L693" s="3"/>
+      <c r="M693" s="3"/>
+    </row>
+    <row r="694" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A694" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="B694" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C694" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D694" s="3">
+        <v>5412882589</v>
+      </c>
+      <c r="E694" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="G694" s="3"/>
+      <c r="H694" s="3"/>
+      <c r="I694" s="3"/>
+      <c r="J694" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K694" s="3"/>
+      <c r="L694" s="3"/>
+      <c r="M694" s="3"/>
+    </row>
+    <row r="695" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A695" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="B695" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C695" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D695" s="3">
+        <v>5413012748</v>
+      </c>
+      <c r="E695" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="G695" s="3"/>
+      <c r="H695" s="3"/>
+      <c r="I695" s="3"/>
+      <c r="J695" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K695" s="3"/>
+      <c r="L695" s="3"/>
+      <c r="M695" s="3"/>
+    </row>
+    <row r="696" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A696" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="B696" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C696" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D696" s="3">
+        <v>5413090805</v>
+      </c>
+      <c r="E696" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G696" s="3"/>
+      <c r="H696" s="3"/>
+      <c r="I696" s="3"/>
+      <c r="J696" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K696" s="3"/>
+      <c r="L696" s="3"/>
+      <c r="M696" s="3"/>
+    </row>
+    <row r="697" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A697" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="B697" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C697" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D697" s="3">
+        <v>5413132447</v>
+      </c>
+      <c r="E697" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="G697" s="3"/>
+      <c r="H697" s="3"/>
+      <c r="I697" s="3"/>
+      <c r="J697" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K697" s="3"/>
+      <c r="L697" s="3"/>
+      <c r="M697" s="3"/>
+    </row>
+    <row r="698" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A698" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="B698" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C698" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D698" s="3">
+        <v>5413256399</v>
+      </c>
+      <c r="E698" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="G698" s="3"/>
+      <c r="H698" s="3"/>
+      <c r="I698" s="3"/>
+      <c r="J698" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K698" s="3"/>
+      <c r="L698" s="3"/>
+      <c r="M698" s="3"/>
+    </row>
+    <row r="699" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A699" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B699" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C699" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D699" s="3">
+        <v>5413335753</v>
+      </c>
+      <c r="E699" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G699" s="3"/>
+      <c r="H699" s="3"/>
+      <c r="I699" s="3"/>
+      <c r="J699" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K699" s="3"/>
+      <c r="L699" s="3"/>
+      <c r="M699" s="3"/>
+    </row>
+    <row r="700" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A700" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="B700" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C700" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D700" s="3">
+        <v>5413343996</v>
+      </c>
+      <c r="E700" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G700" s="3"/>
+      <c r="H700" s="3"/>
+      <c r="I700" s="3"/>
+      <c r="J700" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K700" s="3"/>
+      <c r="L700" s="3"/>
+      <c r="M700" s="3"/>
+    </row>
+    <row r="701" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A701" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="B701" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C701" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D701" s="3">
+        <v>5413393825</v>
+      </c>
+      <c r="E701" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="G701" s="3"/>
+      <c r="H701" s="3"/>
+      <c r="I701" s="3"/>
+      <c r="J701" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K701" s="3"/>
+      <c r="L701" s="3"/>
+      <c r="M701" s="3"/>
+    </row>
+    <row r="702" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A702" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="B702" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C702" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D702" s="3">
+        <v>5418470754</v>
+      </c>
+      <c r="E702" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="G702" s="3"/>
+      <c r="H702" s="3"/>
+      <c r="I702" s="3"/>
+      <c r="J702" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K702" s="3"/>
+      <c r="L702" s="3"/>
+      <c r="M702" s="3"/>
+    </row>
+    <row r="703" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A703" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B703" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C703" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D703" s="3">
+        <v>5418877723</v>
+      </c>
+      <c r="E703" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G703" s="3"/>
+      <c r="H703" s="3"/>
+      <c r="I703" s="3"/>
+      <c r="J703" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K703" s="3"/>
+      <c r="L703" s="3"/>
+      <c r="M703" s="3"/>
+    </row>
+    <row r="704" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A704" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="B704" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C704" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D704" s="3">
+        <v>5418887719</v>
+      </c>
+      <c r="E704" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="G704" s="3"/>
+      <c r="H704" s="3"/>
+      <c r="I704" s="3"/>
+      <c r="J704" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K704" s="3"/>
+      <c r="L704" s="3"/>
+      <c r="M704" s="3"/>
+    </row>
+    <row r="705" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A705" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B705" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C705" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D705" s="3">
+        <v>5418934546</v>
+      </c>
+      <c r="E705" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="G705" s="3"/>
+      <c r="H705" s="3"/>
+      <c r="I705" s="3"/>
+      <c r="J705" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K705" s="3"/>
+      <c r="L705" s="3"/>
+      <c r="M705" s="3"/>
+    </row>
+    <row r="706" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A706" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B706" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C706" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D706" s="3">
+        <v>5419337093</v>
+      </c>
+      <c r="E706" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G706" s="3"/>
+      <c r="H706" s="3"/>
+      <c r="I706" s="3"/>
+      <c r="J706" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K706" s="3"/>
+      <c r="L706" s="3"/>
+      <c r="M706" s="3"/>
+    </row>
+    <row r="707" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A707" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B707" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C707" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D707" s="3">
+        <v>5419364836</v>
+      </c>
+      <c r="E707" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G707" s="3"/>
+      <c r="H707" s="3"/>
+      <c r="I707" s="3"/>
+      <c r="J707" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K707" s="3"/>
+      <c r="L707" s="3"/>
+      <c r="M707" s="3"/>
+    </row>
+    <row r="708" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A708" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B708" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C708" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D708" s="3">
+        <v>5419387817</v>
+      </c>
+      <c r="E708" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F708" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G708" s="3"/>
+      <c r="H708" s="3"/>
+      <c r="I708" s="3"/>
+      <c r="J708" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K708" s="3"/>
+      <c r="L708" s="3"/>
+      <c r="M708" s="3"/>
+    </row>
+    <row r="709" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A709" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B709" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C709" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D709" s="3">
+        <v>5419414275</v>
+      </c>
+      <c r="E709" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F709" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G709" s="3"/>
+      <c r="H709" s="3"/>
+      <c r="I709" s="3"/>
+      <c r="J709" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K709" s="3"/>
+      <c r="L709" s="3"/>
+      <c r="M709" s="3"/>
+    </row>
+    <row r="710" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A710" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B710" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C710" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D710" s="3">
+        <v>5419472394</v>
+      </c>
+      <c r="E710" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F710" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G710" s="3"/>
+      <c r="H710" s="3"/>
+      <c r="I710" s="3"/>
+      <c r="J710" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K710" s="3"/>
+      <c r="L710" s="3"/>
+      <c r="M710" s="3"/>
+    </row>
+    <row r="711" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A711" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B711" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C711" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D711" s="3">
+        <v>5419495287</v>
+      </c>
+      <c r="E711" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="G711" s="3"/>
+      <c r="H711" s="3"/>
+      <c r="I711" s="3"/>
+      <c r="J711" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K711" s="3"/>
+      <c r="L711" s="3"/>
+      <c r="M711" s="3"/>
+    </row>
+    <row r="712" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A712" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B712" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C712" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D712" s="3">
+        <v>5419927592</v>
+      </c>
+      <c r="E712" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G712" s="3"/>
+      <c r="H712" s="3"/>
+      <c r="I712" s="3"/>
+      <c r="J712" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K712" s="3"/>
+      <c r="L712" s="3"/>
+      <c r="M712" s="3"/>
+    </row>
+    <row r="713" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A713" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B713" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C713" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D713" s="3">
+        <v>5420048359</v>
+      </c>
+      <c r="E713" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G713" s="3"/>
+      <c r="H713" s="3"/>
+      <c r="I713" s="3"/>
+      <c r="J713" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K713" s="3"/>
+      <c r="L713" s="3"/>
+      <c r="M713" s="3"/>
+    </row>
+    <row r="714" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A714" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B714" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C714" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D714" s="3">
+        <v>5420199447</v>
+      </c>
+      <c r="E714" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G714" s="3"/>
+      <c r="H714" s="3"/>
+      <c r="I714" s="3"/>
+      <c r="J714" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K714" s="3"/>
+      <c r="L714" s="3"/>
+      <c r="M714" s="3"/>
+    </row>
+    <row r="715" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A715" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B715" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C715" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D715" s="3">
+        <v>5420225951</v>
+      </c>
+      <c r="E715" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="G715" s="3"/>
+      <c r="H715" s="3"/>
+      <c r="I715" s="3"/>
+      <c r="J715" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K715" s="3"/>
+      <c r="L715" s="3"/>
+      <c r="M715" s="3"/>
+    </row>
+    <row r="716" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A716" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B716" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C716" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D716" s="3">
+        <v>5420319849</v>
+      </c>
+      <c r="E716" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G716" s="3"/>
+      <c r="H716" s="3"/>
+      <c r="I716" s="3"/>
+      <c r="J716" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K716" s="3"/>
+      <c r="L716" s="3"/>
+      <c r="M716" s="3"/>
+    </row>
+    <row r="717" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A717" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B717" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C717" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D717" s="3">
+        <v>5420388192</v>
+      </c>
+      <c r="E717" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G717" s="3"/>
+      <c r="H717" s="3"/>
+      <c r="I717" s="3"/>
+      <c r="J717" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K717" s="3"/>
+      <c r="L717" s="3"/>
+      <c r="M717" s="3"/>
+    </row>
+    <row r="718" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A718" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B718" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C718" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D718" s="3">
+        <v>5420417815</v>
+      </c>
+      <c r="E718" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G718" s="3"/>
+      <c r="H718" s="3"/>
+      <c r="I718" s="3"/>
+      <c r="J718" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K718" s="3"/>
+      <c r="L718" s="3"/>
+      <c r="M718" s="3"/>
+    </row>
+    <row r="719" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A719" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B719" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C719" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D719" s="3">
+        <v>5420542407</v>
+      </c>
+      <c r="E719" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G719" s="3"/>
+      <c r="H719" s="3"/>
+      <c r="I719" s="3"/>
+      <c r="J719" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K719" s="3"/>
+      <c r="L719" s="3"/>
+      <c r="M719" s="3"/>
+    </row>
+    <row r="720" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A720" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B720" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C720" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D720" s="3">
+        <v>5420746571</v>
+      </c>
+      <c r="E720" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G720" s="3"/>
+      <c r="H720" s="3"/>
+      <c r="I720" s="3"/>
+      <c r="J720" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K720" s="3"/>
+      <c r="L720" s="3"/>
+      <c r="M720" s="3"/>
+    </row>
+    <row r="721" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A721" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B721" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C721" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D721" s="3">
+        <v>5420842790</v>
+      </c>
+      <c r="E721" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G721" s="3"/>
+      <c r="H721" s="3"/>
+      <c r="I721" s="3"/>
+      <c r="J721" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K721" s="3"/>
+      <c r="L721" s="3"/>
+      <c r="M721" s="3"/>
+    </row>
+    <row r="722" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A722" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B722" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C722" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D722" s="3">
+        <v>5420859452</v>
+      </c>
+      <c r="E722" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G722" s="3"/>
+      <c r="H722" s="3"/>
+      <c r="I722" s="3"/>
+      <c r="J722" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K722" s="3"/>
+      <c r="L722" s="3"/>
+      <c r="M722" s="3"/>
+    </row>
+    <row r="723" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A723" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B723" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C723" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D723" s="3">
+        <v>5420990291</v>
+      </c>
+      <c r="E723" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="G723" s="3"/>
+      <c r="H723" s="3"/>
+      <c r="I723" s="3"/>
+      <c r="J723" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K723" s="3"/>
+      <c r="L723" s="3"/>
+      <c r="M723" s="3"/>
+    </row>
+    <row r="724" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A724" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B724" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C724" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D724" s="3">
+        <v>5421850750</v>
+      </c>
+      <c r="E724" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G724" s="3"/>
+      <c r="H724" s="3"/>
+      <c r="I724" s="3"/>
+      <c r="J724" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K724" s="3"/>
+      <c r="L724" s="3"/>
+      <c r="M724" s="3"/>
+    </row>
+    <row r="725" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A725" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B725" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C725" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D725" s="3">
+        <v>5424355434</v>
+      </c>
+      <c r="E725" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G725" s="3"/>
+      <c r="H725" s="3"/>
+      <c r="I725" s="3"/>
+      <c r="J725" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K725" s="3"/>
+      <c r="L725" s="3"/>
+      <c r="M725" s="3"/>
+    </row>
+    <row r="726" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A726" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B726" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C726" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D726" s="3">
+        <v>5424390557</v>
+      </c>
+      <c r="E726" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G726" s="3"/>
+      <c r="H726" s="3"/>
+      <c r="I726" s="3"/>
+      <c r="J726" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K726" s="3"/>
+      <c r="L726" s="3"/>
+      <c r="M726" s="3"/>
+    </row>
+    <row r="727" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A727" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B727" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C727" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D727" s="3">
+        <v>5424442748</v>
+      </c>
+      <c r="E727" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H727" s="3"/>
+      <c r="I727" s="3"/>
+      <c r="J727" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K727" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L727" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="M727" s="3"/>
+    </row>
+    <row r="728" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A728" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B728" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C728" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D728" s="3">
+        <v>5424847801</v>
+      </c>
+      <c r="E728" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="G728" s="3"/>
+      <c r="H728" s="3"/>
+      <c r="I728" s="3"/>
+      <c r="J728" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K728" s="3"/>
+      <c r="L728" s="3"/>
+      <c r="M728" s="3"/>
+    </row>
+    <row r="729" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A729" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B729" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C729" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D729" s="3">
+        <v>5425265882</v>
+      </c>
+      <c r="E729" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="G729" s="3"/>
+      <c r="H729" s="3"/>
+      <c r="I729" s="3"/>
+      <c r="J729" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K729" s="3"/>
+      <c r="L729" s="3"/>
+      <c r="M729" s="3"/>
+    </row>
+    <row r="730" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A730" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B730" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C730" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D730" s="3">
+        <v>5425445173</v>
+      </c>
+      <c r="E730" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G730" s="3"/>
+      <c r="H730" s="3"/>
+      <c r="I730" s="3"/>
+      <c r="J730" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K730" s="3"/>
+      <c r="L730" s="3"/>
+      <c r="M730" s="3"/>
+    </row>
+    <row r="731" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A731" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B731" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C731" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D731" s="3">
+        <v>5425833871</v>
+      </c>
+      <c r="E731" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G731" s="3"/>
+      <c r="H731" s="3"/>
+      <c r="I731" s="3"/>
+      <c r="J731" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K731" s="3"/>
+      <c r="L731" s="3"/>
+      <c r="M731" s="3"/>
+    </row>
+    <row r="732" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A732" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B732" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C732" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D732" s="3">
+        <v>5426217889</v>
+      </c>
+      <c r="E732" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G732" s="3"/>
+      <c r="H732" s="3"/>
+      <c r="I732" s="3"/>
+      <c r="J732" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K732" s="3"/>
+      <c r="L732" s="3"/>
+      <c r="M732" s="3"/>
+    </row>
+    <row r="733" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A733" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B733" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C733" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D733" s="3">
+        <v>5426681798</v>
+      </c>
+      <c r="E733" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G733" s="3"/>
+      <c r="H733" s="3"/>
+      <c r="I733" s="3"/>
+      <c r="J733" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K733" s="3"/>
+      <c r="L733" s="3"/>
+      <c r="M733" s="3"/>
+    </row>
+    <row r="734" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A734" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B734" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C734" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D734" s="3">
+        <v>5426802114</v>
+      </c>
+      <c r="E734" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F734" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G734" s="3"/>
+      <c r="H734" s="3"/>
+      <c r="I734" s="3"/>
+      <c r="J734" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K734" s="3"/>
+      <c r="L734" s="3"/>
+      <c r="M734" s="3"/>
+    </row>
+    <row r="735" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A735" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B735" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C735" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D735" s="3">
+        <v>5426811166</v>
+      </c>
+      <c r="E735" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F735" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G735" s="3"/>
+      <c r="H735" s="3"/>
+      <c r="I735" s="3"/>
+      <c r="J735" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K735" s="3"/>
+      <c r="L735" s="3"/>
+      <c r="M735" s="3"/>
+    </row>
+    <row r="736" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A736" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B736" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C736" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D736" s="3">
+        <v>5426820761</v>
+      </c>
+      <c r="E736" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F736" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G736" s="3"/>
+      <c r="H736" s="3"/>
+      <c r="I736" s="3"/>
+      <c r="J736" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K736" s="3"/>
+      <c r="L736" s="3"/>
+      <c r="M736" s="3"/>
+    </row>
+    <row r="737" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A737" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B737" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C737" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D737" s="3">
+        <v>5426846569</v>
+      </c>
+      <c r="E737" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G737" s="3"/>
+      <c r="H737" s="3"/>
+      <c r="I737" s="3"/>
+      <c r="J737" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K737" s="3"/>
+      <c r="L737" s="3"/>
+      <c r="M737" s="3"/>
+    </row>
+    <row r="738" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A738" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B738" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C738" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D738" s="3">
+        <v>5426880891</v>
+      </c>
+      <c r="E738" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G738" s="3"/>
+      <c r="H738" s="3"/>
+      <c r="I738" s="3"/>
+      <c r="J738" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K738" s="3"/>
+      <c r="L738" s="3"/>
+      <c r="M738" s="3"/>
+    </row>
+    <row r="739" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A739" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B739" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C739" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D739" s="3">
+        <v>5427254335</v>
+      </c>
+      <c r="E739" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G739" s="3"/>
+      <c r="H739" s="3"/>
+      <c r="I739" s="3"/>
+      <c r="J739" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K739" s="3"/>
+      <c r="L739" s="3"/>
+      <c r="M739" s="3"/>
+    </row>
+    <row r="740" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A740" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B740" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C740" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D740" s="3">
+        <v>5427263061</v>
+      </c>
+      <c r="E740" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G740" s="3"/>
+      <c r="H740" s="3"/>
+      <c r="I740" s="3"/>
+      <c r="J740" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K740" s="3"/>
+      <c r="L740" s="3"/>
+      <c r="M740" s="3"/>
+    </row>
+    <row r="741" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A741" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B741" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C741" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D741" s="3">
+        <v>5427272676</v>
+      </c>
+      <c r="E741" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F741" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="G741" s="3"/>
+      <c r="H741" s="3"/>
+      <c r="I741" s="3"/>
+      <c r="J741" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K741" s="3"/>
+      <c r="L741" s="3"/>
+      <c r="M741" s="3"/>
+    </row>
+    <row r="742" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A742" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B742" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C742" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D742" s="3">
+        <v>5427270889</v>
+      </c>
+      <c r="E742" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F742" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G742" s="3"/>
+      <c r="H742" s="3"/>
+      <c r="I742" s="3"/>
+      <c r="J742" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K742" s="3"/>
+      <c r="L742" s="3"/>
+      <c r="M742" s="3"/>
+    </row>
+    <row r="743" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A743" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B743" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C743" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D743" s="3">
+        <v>5427287957</v>
+      </c>
+      <c r="E743" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F743" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G743" s="3"/>
+      <c r="H743" s="3"/>
+      <c r="I743" s="3"/>
+      <c r="J743" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K743" s="3"/>
+      <c r="L743" s="3"/>
+      <c r="M743" s="3"/>
+    </row>
+    <row r="744" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A744" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B744" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C744" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D744" s="3">
+        <v>5427405089</v>
+      </c>
+      <c r="E744" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F744" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G744" s="3"/>
+      <c r="H744" s="3"/>
+      <c r="I744" s="3"/>
+      <c r="J744" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K744" s="3"/>
+      <c r="L744" s="3"/>
+      <c r="M744" s="3"/>
+    </row>
+    <row r="745" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A745" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B745" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C745" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D745" s="3">
+        <v>5430738726</v>
+      </c>
+      <c r="E745" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F745" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G745" s="3"/>
+      <c r="H745" s="3"/>
+      <c r="I745" s="3"/>
+      <c r="J745" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K745" s="3"/>
+      <c r="L745" s="3"/>
+      <c r="M745" s="3"/>
+    </row>
+    <row r="746" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A746" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B746" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C746" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D746" s="3">
+        <v>5430854137</v>
+      </c>
+      <c r="E746" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="G746" s="3"/>
+      <c r="H746" s="3"/>
+      <c r="I746" s="3"/>
+      <c r="J746" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K746" s="3"/>
+      <c r="L746" s="3"/>
+      <c r="M746" s="3"/>
+    </row>
+    <row r="747" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A747" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B747" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C747" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D747" s="3">
+        <v>5431263438</v>
+      </c>
+      <c r="E747" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F747" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G747" s="3"/>
+      <c r="H747" s="3"/>
+      <c r="I747" s="3"/>
+      <c r="J747" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K747" s="3"/>
+      <c r="L747" s="3"/>
+      <c r="M747" s="3"/>
+    </row>
+    <row r="748" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A748" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B748" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C748" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D748" s="3">
+        <v>5431265169</v>
+      </c>
+      <c r="E748" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G748" s="3"/>
+      <c r="H748" s="3"/>
+      <c r="I748" s="3"/>
+      <c r="J748" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K748" s="3"/>
+      <c r="L748" s="3"/>
+      <c r="M748" s="3"/>
+    </row>
+    <row r="749" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A749" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B749" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C749" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D749" s="3">
+        <v>5431282314</v>
+      </c>
+      <c r="E749" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F749" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G749" s="3"/>
+      <c r="H749" s="3"/>
+      <c r="I749" s="3"/>
+      <c r="J749" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K749" s="3"/>
+      <c r="L749" s="3"/>
+      <c r="M749" s="3"/>
+    </row>
+    <row r="750" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A750" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B750" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C750" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D750" s="3">
+        <v>5431303027</v>
+      </c>
+      <c r="E750" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G750" s="3"/>
+      <c r="H750" s="3"/>
+      <c r="I750" s="3"/>
+      <c r="J750" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K750" s="3"/>
+      <c r="L750" s="3"/>
+      <c r="M750" s="3"/>
+    </row>
+    <row r="751" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A751" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B751" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C751" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D751" s="3">
+        <v>5431462426</v>
+      </c>
+      <c r="E751" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F751" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G751" s="3"/>
+      <c r="H751" s="3"/>
+      <c r="I751" s="3"/>
+      <c r="J751" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K751" s="3"/>
+      <c r="L751" s="3"/>
+      <c r="M751" s="3"/>
+    </row>
+    <row r="752" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A752" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B752" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C752" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D752" s="3">
+        <v>5431488244</v>
+      </c>
+      <c r="E752" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G752" s="3"/>
+      <c r="H752" s="3"/>
+      <c r="I752" s="3"/>
+      <c r="J752" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K752" s="3"/>
+      <c r="L752" s="3"/>
+      <c r="M752" s="3"/>
+    </row>
+    <row r="753" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A753" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B753" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C753" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D753" s="3">
+        <v>5431620279</v>
+      </c>
+      <c r="E753" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F753" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G753" s="3"/>
+      <c r="H753" s="3"/>
+      <c r="I753" s="3"/>
+      <c r="J753" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K753" s="3"/>
+      <c r="L753" s="3"/>
+      <c r="M753" s="3"/>
+    </row>
+    <row r="754" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A754" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B754" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C754" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D754" s="3">
+        <v>5431817505</v>
+      </c>
+      <c r="E754" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F754" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G754" s="3"/>
+      <c r="H754" s="3"/>
+      <c r="I754" s="3"/>
+      <c r="J754" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K754" s="3"/>
+      <c r="L754" s="3"/>
+      <c r="M754" s="3"/>
+    </row>
+    <row r="755" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A755" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B755" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C755" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D755" s="3">
+        <v>5431849481</v>
+      </c>
+      <c r="E755" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F755" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="G755" s="3"/>
+      <c r="H755" s="3"/>
+      <c r="I755" s="3"/>
+      <c r="J755" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K755" s="3"/>
+      <c r="L755" s="3"/>
+      <c r="M755" s="3"/>
+    </row>
+    <row r="756" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A756" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B756" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C756" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D756" s="3">
+        <v>5431866764</v>
+      </c>
+      <c r="E756" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F756" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G756" s="3"/>
+      <c r="H756" s="3"/>
+      <c r="I756" s="3"/>
+      <c r="J756" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K756" s="3"/>
+      <c r="L756" s="3"/>
+      <c r="M756" s="3"/>
+    </row>
+    <row r="757" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A757" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B757" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C757" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D757" s="3">
+        <v>5431880753</v>
+      </c>
+      <c r="E757" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F757" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G757" s="3"/>
+      <c r="H757" s="3"/>
+      <c r="I757" s="3"/>
+      <c r="J757" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K757" s="3"/>
+      <c r="L757" s="3"/>
+      <c r="M757" s="3"/>
+    </row>
+    <row r="758" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A758" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B758" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C758" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D758" s="3">
+        <v>5431897790</v>
+      </c>
+      <c r="E758" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F758" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="G758" s="3"/>
+      <c r="H758" s="3"/>
+      <c r="I758" s="3"/>
+      <c r="J758" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K758" s="3"/>
+      <c r="L758" s="3"/>
+      <c r="M758" s="3"/>
+    </row>
+    <row r="759" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A759" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B759" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C759" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D759" s="3">
+        <v>5432146119</v>
+      </c>
+      <c r="E759" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F759" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="G759" s="3"/>
+      <c r="H759" s="3"/>
+      <c r="I759" s="3"/>
+      <c r="J759" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K759" s="3"/>
+      <c r="L759" s="3"/>
+      <c r="M759" s="3"/>
+    </row>
+    <row r="760" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A760" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B760" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C760" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D760" s="3">
+        <v>5432160491</v>
+      </c>
+      <c r="E760" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F760" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G760" s="3"/>
+      <c r="H760" s="3"/>
+      <c r="I760" s="3"/>
+      <c r="J760" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K760" s="3"/>
+      <c r="L760" s="3"/>
+      <c r="M760" s="3"/>
+    </row>
+    <row r="761" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A761" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B761" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="C761" s="3"/>
+      <c r="D761" s="3">
+        <v>5432427823</v>
+      </c>
+      <c r="E761" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F761" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G761" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H761" s="3"/>
+      <c r="I761" s="3"/>
+      <c r="J761" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K761" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L761" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="M761" s="3"/>
+    </row>
+    <row r="762" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A762" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B762" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C762" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D762" s="3">
+        <v>5433048566</v>
+      </c>
+      <c r="E762" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F762" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G762" s="3"/>
+      <c r="H762" s="3"/>
+      <c r="I762" s="3"/>
+      <c r="J762" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K762" s="3"/>
+      <c r="L762" s="3"/>
+      <c r="M762" s="3"/>
+    </row>
+    <row r="763" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A763" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B763" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C763" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D763" s="3">
+        <v>5437138344</v>
+      </c>
+      <c r="E763" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F763" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="G763" s="3"/>
+      <c r="H763" s="3"/>
+      <c r="I763" s="3"/>
+      <c r="J763" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K763" s="3"/>
+      <c r="L763" s="3"/>
+      <c r="M763" s="3"/>
+    </row>
+    <row r="764" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A764" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B764" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C764" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D764" s="3">
+        <v>5437214822</v>
+      </c>
+      <c r="E764" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F764" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G764" s="3"/>
+      <c r="H764" s="3"/>
+      <c r="I764" s="3"/>
+      <c r="J764" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K764" s="3"/>
+      <c r="L764" s="3"/>
+      <c r="M764" s="3"/>
+    </row>
+    <row r="765" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A765" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B765" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C765" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D765" s="3">
+        <v>5437275736</v>
+      </c>
+      <c r="E765" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F765" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G765" s="3"/>
+      <c r="H765" s="3"/>
+      <c r="I765" s="3"/>
+      <c r="J765" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K765" s="3"/>
+      <c r="L765" s="3"/>
+      <c r="M765" s="3"/>
+    </row>
+    <row r="766" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A766" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B766" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C766" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D766" s="3">
+        <v>5437396717</v>
+      </c>
+      <c r="E766" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F766" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G766" s="3"/>
+      <c r="H766" s="3"/>
+      <c r="I766" s="3"/>
+      <c r="J766" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K766" s="3"/>
+      <c r="L766" s="3"/>
+      <c r="M766" s="3"/>
+    </row>
+    <row r="767" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A767" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B767" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C767" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D767" s="3">
+        <v>5437407814</v>
+      </c>
+      <c r="E767" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F767" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G767" s="3"/>
+      <c r="H767" s="3"/>
+      <c r="I767" s="3"/>
+      <c r="J767" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K767" s="3"/>
+      <c r="L767" s="3"/>
+      <c r="M767" s="3"/>
+    </row>
+    <row r="768" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A768" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B768" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C768" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D768" s="3">
+        <v>5437430096</v>
+      </c>
+      <c r="E768" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F768" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G768" s="3"/>
+      <c r="H768" s="3"/>
+      <c r="I768" s="3"/>
+      <c r="J768" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K768" s="3"/>
+      <c r="L768" s="3"/>
+      <c r="M768" s="3"/>
+    </row>
+    <row r="769" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A769" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B769" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C769" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D769" s="3">
+        <v>5437478527</v>
+      </c>
+      <c r="E769" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F769" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G769" s="3"/>
+      <c r="H769" s="3"/>
+      <c r="I769" s="3"/>
+      <c r="J769" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K769" s="3"/>
+      <c r="L769" s="3"/>
+      <c r="M769" s="3"/>
+    </row>
+    <row r="770" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A770" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B770" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C770" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D770" s="3">
+        <v>5437550217</v>
+      </c>
+      <c r="E770" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F770" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G770" s="3"/>
+      <c r="H770" s="3"/>
+      <c r="I770" s="3"/>
+      <c r="J770" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K770" s="3"/>
+      <c r="L770" s="3"/>
+      <c r="M770" s="3"/>
+    </row>
+    <row r="771" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A771" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B771" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C771" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D771" s="3">
+        <v>5437680914</v>
+      </c>
+      <c r="E771" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F771" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G771" s="3"/>
+      <c r="H771" s="3"/>
+      <c r="I771" s="3"/>
+      <c r="J771" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K771" s="3"/>
+      <c r="L771" s="3"/>
+      <c r="M771" s="3"/>
+    </row>
+    <row r="772" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A772" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B772" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C772" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D772" s="3">
+        <v>5437831684</v>
+      </c>
+      <c r="E772" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F772" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G772" s="3"/>
+      <c r="H772" s="3"/>
+      <c r="I772" s="3"/>
+      <c r="J772" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K772" s="3"/>
+      <c r="L772" s="3"/>
+      <c r="M772" s="3"/>
+    </row>
+    <row r="773" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A773" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B773" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C773" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D773" s="3">
+        <v>5437895139</v>
+      </c>
+      <c r="E773" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F773" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G773" s="3"/>
+      <c r="H773" s="3"/>
+      <c r="I773" s="3"/>
+      <c r="J773" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K773" s="3"/>
+      <c r="L773" s="3"/>
+      <c r="M773" s="3"/>
+    </row>
+    <row r="774" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A774" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B774" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C774" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D774" s="3">
+        <v>5437917130</v>
+      </c>
+      <c r="E774" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F774" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G774" s="3"/>
+      <c r="H774" s="3"/>
+      <c r="I774" s="3"/>
+      <c r="J774" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K774" s="3"/>
+      <c r="L774" s="3"/>
+      <c r="M774" s="3"/>
+    </row>
+    <row r="775" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A775" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B775" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C775" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D775" s="3">
+        <v>5437975423</v>
+      </c>
+      <c r="E775" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F775" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G775" s="3"/>
+      <c r="H775" s="3"/>
+      <c r="I775" s="3"/>
+      <c r="J775" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K775" s="3"/>
+      <c r="L775" s="3"/>
+      <c r="M775" s="3"/>
+    </row>
+    <row r="776" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A776" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B776" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C776" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D776" s="3">
+        <v>5438130006</v>
+      </c>
+      <c r="E776" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F776" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G776" s="3"/>
+      <c r="H776" s="3"/>
+      <c r="I776" s="3"/>
+      <c r="J776" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K776" s="3"/>
+      <c r="L776" s="3"/>
+      <c r="M776" s="3"/>
+    </row>
+    <row r="777" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A777" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B777" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C777" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D777" s="3">
+        <v>5438493276</v>
+      </c>
+      <c r="E777" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F777" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G777" s="3"/>
+      <c r="H777" s="3"/>
+      <c r="I777" s="3"/>
+      <c r="J777" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K777" s="3"/>
+      <c r="L777" s="3"/>
+      <c r="M777" s="3"/>
+    </row>
+    <row r="778" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A778" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B778" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C778" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D778" s="3">
+        <v>5439116921</v>
+      </c>
+      <c r="E778" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F778" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="G778" s="3"/>
+      <c r="H778" s="3"/>
+      <c r="I778" s="3"/>
+      <c r="J778" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K778" s="3"/>
+      <c r="L778" s="3"/>
+      <c r="M778" s="3"/>
+    </row>
+    <row r="779" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A779" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B779" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C779" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D779" s="3">
+        <v>5439258272</v>
+      </c>
+      <c r="E779" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F779" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G779" s="3"/>
+      <c r="H779" s="3"/>
+      <c r="I779" s="3"/>
+      <c r="J779" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K779" s="3"/>
+      <c r="L779" s="3"/>
+      <c r="M779" s="3"/>
+    </row>
+    <row r="780" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A780" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B780" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C780" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D780" s="3">
+        <v>5439368989</v>
+      </c>
+      <c r="E780" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F780" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="G780" s="3"/>
+      <c r="H780" s="3"/>
+      <c r="I780" s="3"/>
+      <c r="J780" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K780" s="3"/>
+      <c r="L780" s="3"/>
+      <c r="M780" s="3"/>
+    </row>
+    <row r="781" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A781" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B781" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C781" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D781" s="3">
+        <v>5439482102</v>
+      </c>
+      <c r="E781" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F781" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="G781" s="3"/>
+      <c r="H781" s="3"/>
+      <c r="I781" s="3"/>
+      <c r="J781" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K781" s="3"/>
+      <c r="L781" s="3"/>
+      <c r="M781" s="3"/>
+    </row>
+    <row r="782" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A782" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B782" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C782" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D782" s="3">
+        <v>5439528236</v>
+      </c>
+      <c r="E782" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F782" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G782" s="3"/>
+      <c r="H782" s="3"/>
+      <c r="I782" s="3"/>
+      <c r="J782" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K782" s="3"/>
+      <c r="L782" s="3"/>
+      <c r="M782" s="3"/>
+    </row>
+    <row r="783" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A783" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B783" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C783" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D783" s="3">
+        <v>5440196067</v>
+      </c>
+      <c r="E783" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F783" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G783" s="3"/>
+      <c r="H783" s="3"/>
+      <c r="I783" s="3"/>
+      <c r="J783" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K783" s="3"/>
+      <c r="L783" s="3"/>
+      <c r="M783" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Starkey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51B30933-2D70-4EE6-B75D-677F93FDF8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC1EBB97-081D-435C-8801-B752A3BB1CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14656" uniqueCount="3030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15495" uniqueCount="3184">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -9110,6 +9110,468 @@
   </si>
   <si>
     <t>04/13/26 09:17 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 10:01 EDT</t>
+  </si>
+  <si>
+    <t>6.9mi S of Amarillo TX</t>
+  </si>
+  <si>
+    <t>04/14/26 09:31 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 10:16 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 10:42 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 10:44 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 11:00 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 11:17 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 11:46 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 11:54 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 09:32 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 12:32 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 12:34 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 12:46 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 13:44 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 08:29 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 10:17 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 10:22 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 10:25 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 10:37 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 07:57 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 10:40 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 10:41 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 10:43 EDT</t>
+  </si>
+  <si>
+    <t>Tanner Rodgers</t>
+  </si>
+  <si>
+    <t>04/15/26 08:00 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 10:51 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 11:10 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 11:18 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 11:20 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 11:23 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 11:50 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 12:16 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 12:19 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 12:20 EDT</t>
+  </si>
+  <si>
+    <t>7.8mi NW of Amarillo TX</t>
+  </si>
+  <si>
+    <t>04/14/26 12:40 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 12:54 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 13:11 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 13:13 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 13:14 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 13:15 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 13:21 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 13:46 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 13:53 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 13:57 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 14:01 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 14:10 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 14:12 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 15:04 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 15:13 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 15:18 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 15:28 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 15:34 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 15:40 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 15:42 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 15:45 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 08:39 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 08:41 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 09:10 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 08:57 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 08:58 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi SW of Amarillo TX</t>
+  </si>
+  <si>
+    <t>04/15/26 08:59 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi SW of Amarillo TX</t>
+  </si>
+  <si>
+    <t>04/15/26 09:16 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 10:21 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 10:29 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 10:48 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 11:01 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 11:15 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 11:21 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 11:43 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 12:00 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 12:06 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 12:11 EDT</t>
+  </si>
+  <si>
+    <t>10.1mi NE of Canyon TX</t>
+  </si>
+  <si>
+    <t>04/15/26 12:18 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 12:36 EDT</t>
+  </si>
+  <si>
+    <t>10.2mi SE of Amarillo TX</t>
+  </si>
+  <si>
+    <t>04/15/26 13:12 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 13:44 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 13:47 EDT</t>
+  </si>
+  <si>
+    <t>9.5mi SE of Amarillo TX</t>
+  </si>
+  <si>
+    <t>04/15/26 14:57 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 15:00 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 15:35 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 15:38 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 09:12 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 16:22 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 08:30 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 08:49 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 09:04 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 09:17 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 09:19 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 10:12 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 07:32 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 10:31 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 10:32 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 10:43 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 10:54 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 11:03 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 11:04 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 11:18 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 11:22 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 11:33 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 11:35 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 11:51 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 11:54 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 12:06 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 12:20 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 12:53 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 13:16 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 13:34 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 13:43 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 13:53 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 13:57 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 14:15 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 14:30 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 14:36 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 15:18 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 08:56 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 09:00 EDT</t>
+  </si>
+  <si>
+    <t>0.7mi N of Canyon TX</t>
+  </si>
+  <si>
+    <t>04/17/26 09:13 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 09:33 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 09:45 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 09:54 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 10:04 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 10:11 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 10:16 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 10:31 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 10:58 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 11:14 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 11:18 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 11:25 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 11:45 EDT</t>
+  </si>
+  <si>
+    <t>11.9mi E of Canyon TX</t>
+  </si>
+  <si>
+    <t>04/17/26 11:50 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 12:04 EDT</t>
+  </si>
+  <si>
+    <t>4.4mi SE of Canyon TX</t>
+  </si>
+  <si>
+    <t>04/17/26 12:07 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 12:10 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 12:11 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 12:16 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 12:42 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 13:01 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 13:02 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 13:18 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 13:47 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 14:00 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 14:24 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 14:58 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 15:13 EDT</t>
   </si>
 </sst>
 </file>
@@ -9471,7 +9933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2465"/>
+  <dimension ref="A1:M2608"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -13731,19 +14193,19 @@
         <v>290</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D148" s="3">
-        <v>5034778913</v>
+        <v>5034778294</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="G148" s="3"/>
       <c r="H148" s="3"/>
@@ -13760,19 +14222,19 @@
         <v>290</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D149" s="3">
-        <v>5034778294</v>
+        <v>5034778913</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="G149" s="3"/>
       <c r="H149" s="3"/>
@@ -80736,6 +81198,4119 @@
       <c r="L2465" s="3"/>
       <c r="M2465" s="3"/>
     </row>
+    <row r="2466" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2466" s="3" t="s">
+        <v>3030</v>
+      </c>
+      <c r="B2466" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2466" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2466" s="3">
+        <v>5569382230</v>
+      </c>
+      <c r="E2466" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2466" s="3" t="s">
+        <v>3031</v>
+      </c>
+      <c r="G2466" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2466" s="3"/>
+      <c r="I2466" s="3"/>
+      <c r="J2466" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2466" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2466" s="3" t="s">
+        <v>3032</v>
+      </c>
+      <c r="M2466" s="3"/>
+    </row>
+    <row r="2467" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2467" s="3" t="s">
+        <v>3033</v>
+      </c>
+      <c r="B2467" s="3"/>
+      <c r="C2467" s="3"/>
+      <c r="D2467" s="3">
+        <v>5569467356</v>
+      </c>
+      <c r="E2467" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2467" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2467" s="3"/>
+      <c r="H2467" s="3"/>
+      <c r="I2467" s="3"/>
+      <c r="J2467" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2467" s="3"/>
+      <c r="L2467" s="3"/>
+      <c r="M2467" s="3"/>
+    </row>
+    <row r="2468" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2468" s="3" t="s">
+        <v>3034</v>
+      </c>
+      <c r="B2468" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2468" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2468" s="3">
+        <v>5569695559</v>
+      </c>
+      <c r="E2468" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2468" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2468" s="3"/>
+      <c r="H2468" s="3"/>
+      <c r="I2468" s="3"/>
+      <c r="J2468" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2468" s="3"/>
+      <c r="L2468" s="3"/>
+      <c r="M2468" s="3"/>
+    </row>
+    <row r="2469" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2469" s="3" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B2469" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2469" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2469" s="3">
+        <v>5569637866</v>
+      </c>
+      <c r="E2469" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2469" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="G2469" s="3"/>
+      <c r="H2469" s="3"/>
+      <c r="I2469" s="3"/>
+      <c r="J2469" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2469" s="3"/>
+      <c r="L2469" s="3"/>
+      <c r="M2469" s="3"/>
+    </row>
+    <row r="2470" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2470" s="3" t="s">
+        <v>3036</v>
+      </c>
+      <c r="B2470" s="3"/>
+      <c r="C2470" s="3"/>
+      <c r="D2470" s="3">
+        <v>5569743701</v>
+      </c>
+      <c r="E2470" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2470" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2470" s="3"/>
+      <c r="H2470" s="3"/>
+      <c r="I2470" s="3"/>
+      <c r="J2470" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2470" s="3"/>
+      <c r="L2470" s="3"/>
+      <c r="M2470" s="3"/>
+    </row>
+    <row r="2471" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2471" s="3" t="s">
+        <v>3037</v>
+      </c>
+      <c r="B2471" s="3"/>
+      <c r="C2471" s="3"/>
+      <c r="D2471" s="3">
+        <v>5569860449</v>
+      </c>
+      <c r="E2471" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2471" s="3" t="s">
+        <v>1795</v>
+      </c>
+      <c r="G2471" s="3"/>
+      <c r="H2471" s="3"/>
+      <c r="I2471" s="3"/>
+      <c r="J2471" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2471" s="3"/>
+      <c r="L2471" s="3"/>
+      <c r="M2471" s="3"/>
+    </row>
+    <row r="2472" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2472" s="3" t="s">
+        <v>3038</v>
+      </c>
+      <c r="B2472" s="3"/>
+      <c r="C2472" s="3"/>
+      <c r="D2472" s="3">
+        <v>5570074731</v>
+      </c>
+      <c r="E2472" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2472" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="G2472" s="3"/>
+      <c r="H2472" s="3"/>
+      <c r="I2472" s="3"/>
+      <c r="J2472" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2472" s="3"/>
+      <c r="L2472" s="3"/>
+      <c r="M2472" s="3"/>
+    </row>
+    <row r="2473" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2473" s="3" t="s">
+        <v>3039</v>
+      </c>
+      <c r="B2473" s="3"/>
+      <c r="C2473" s="3"/>
+      <c r="D2473" s="3">
+        <v>5570134613</v>
+      </c>
+      <c r="E2473" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2473" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2473" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2473" s="3"/>
+      <c r="I2473" s="3"/>
+      <c r="J2473" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2473" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2473" s="3" t="s">
+        <v>3040</v>
+      </c>
+      <c r="M2473" s="3"/>
+    </row>
+    <row r="2474" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2474" s="3" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B2474" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2474" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2474" s="3">
+        <v>5570439959</v>
+      </c>
+      <c r="E2474" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2474" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="G2474" s="3"/>
+      <c r="H2474" s="3"/>
+      <c r="I2474" s="3"/>
+      <c r="J2474" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2474" s="3"/>
+      <c r="L2474" s="3"/>
+      <c r="M2474" s="3"/>
+    </row>
+    <row r="2475" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2475" s="3" t="s">
+        <v>3042</v>
+      </c>
+      <c r="B2475" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2475" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2475" s="3">
+        <v>5570455905</v>
+      </c>
+      <c r="E2475" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2475" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="G2475" s="3"/>
+      <c r="H2475" s="3"/>
+      <c r="I2475" s="3"/>
+      <c r="J2475" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2475" s="3"/>
+      <c r="L2475" s="3"/>
+      <c r="M2475" s="3"/>
+    </row>
+    <row r="2476" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2476" s="3" t="s">
+        <v>3043</v>
+      </c>
+      <c r="B2476" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2476" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2476" s="3">
+        <v>5570553490</v>
+      </c>
+      <c r="E2476" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2476" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2476" s="3"/>
+      <c r="H2476" s="3"/>
+      <c r="I2476" s="3"/>
+      <c r="J2476" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2476" s="3"/>
+      <c r="L2476" s="3"/>
+      <c r="M2476" s="3"/>
+    </row>
+    <row r="2477" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2477" s="3" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B2477" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2477" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2477" s="3">
+        <v>5571037637</v>
+      </c>
+      <c r="E2477" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2477" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2477" s="3"/>
+      <c r="H2477" s="3"/>
+      <c r="I2477" s="3"/>
+      <c r="J2477" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2477" s="3"/>
+      <c r="L2477" s="3"/>
+      <c r="M2477" s="3"/>
+    </row>
+    <row r="2478" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2478" s="3" t="s">
+        <v>3045</v>
+      </c>
+      <c r="B2478" s="3"/>
+      <c r="C2478" s="3"/>
+      <c r="D2478" s="3">
+        <v>5575431613</v>
+      </c>
+      <c r="E2478" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2478" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2478" s="3"/>
+      <c r="H2478" s="3"/>
+      <c r="I2478" s="3"/>
+      <c r="J2478" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2478" s="3"/>
+      <c r="L2478" s="3"/>
+      <c r="M2478" s="3"/>
+    </row>
+    <row r="2479" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2479" s="3" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2479" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2479" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2479" s="3">
+        <v>5575741358</v>
+      </c>
+      <c r="E2479" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2479" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G2479" s="3"/>
+      <c r="H2479" s="3"/>
+      <c r="I2479" s="3"/>
+      <c r="J2479" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2479" s="3"/>
+      <c r="L2479" s="3"/>
+      <c r="M2479" s="3"/>
+    </row>
+    <row r="2480" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2480" s="3" t="s">
+        <v>3046</v>
+      </c>
+      <c r="B2480" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2480" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2480" s="3">
+        <v>5575998722</v>
+      </c>
+      <c r="E2480" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2480" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2480" s="3"/>
+      <c r="H2480" s="3"/>
+      <c r="I2480" s="3"/>
+      <c r="J2480" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2480" s="3"/>
+      <c r="L2480" s="3"/>
+      <c r="M2480" s="3"/>
+    </row>
+    <row r="2481" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2481" s="3" t="s">
+        <v>3047</v>
+      </c>
+      <c r="B2481" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2481" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2481" s="3">
+        <v>5576029055</v>
+      </c>
+      <c r="E2481" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2481" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="G2481" s="3"/>
+      <c r="H2481" s="3"/>
+      <c r="I2481" s="3"/>
+      <c r="J2481" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2481" s="3"/>
+      <c r="L2481" s="3"/>
+      <c r="M2481" s="3"/>
+    </row>
+    <row r="2482" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2482" s="3" t="s">
+        <v>3048</v>
+      </c>
+      <c r="B2482" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2482" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2482" s="3">
+        <v>5576047671</v>
+      </c>
+      <c r="E2482" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2482" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2482" s="3"/>
+      <c r="H2482" s="3"/>
+      <c r="I2482" s="3"/>
+      <c r="J2482" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2482" s="3"/>
+      <c r="L2482" s="3"/>
+      <c r="M2482" s="3"/>
+    </row>
+    <row r="2483" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2483" s="3" t="s">
+        <v>3049</v>
+      </c>
+      <c r="B2483" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2483" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2483" s="3">
+        <v>5576122542</v>
+      </c>
+      <c r="E2483" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2483" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="G2483" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2483" s="3"/>
+      <c r="I2483" s="3"/>
+      <c r="J2483" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2483" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2483" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="M2483" s="3"/>
+    </row>
+    <row r="2484" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2484" s="3" t="s">
+        <v>3051</v>
+      </c>
+      <c r="B2484" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2484" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2484" s="3">
+        <v>5576141905</v>
+      </c>
+      <c r="E2484" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2484" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G2484" s="3"/>
+      <c r="H2484" s="3"/>
+      <c r="I2484" s="3"/>
+      <c r="J2484" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2484" s="3"/>
+      <c r="L2484" s="3"/>
+      <c r="M2484" s="3"/>
+    </row>
+    <row r="2485" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2485" s="3" t="s">
+        <v>3052</v>
+      </c>
+      <c r="B2485" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2485" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2485" s="3">
+        <v>5576148326</v>
+      </c>
+      <c r="E2485" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2485" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G2485" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2485" s="3"/>
+      <c r="I2485" s="3"/>
+      <c r="J2485" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2485" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2485" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="M2485" s="3"/>
+    </row>
+    <row r="2486" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2486" s="3" t="s">
+        <v>3053</v>
+      </c>
+      <c r="B2486" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2486" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2486" s="3">
+        <v>5576161509</v>
+      </c>
+      <c r="E2486" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2486" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G2486" s="3"/>
+      <c r="H2486" s="3"/>
+      <c r="I2486" s="3"/>
+      <c r="J2486" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2486" s="3"/>
+      <c r="L2486" s="3"/>
+      <c r="M2486" s="3"/>
+    </row>
+    <row r="2487" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2487" s="3" t="s">
+        <v>3053</v>
+      </c>
+      <c r="B2487" s="3" t="s">
+        <v>3054</v>
+      </c>
+      <c r="C2487" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2487" s="3">
+        <v>5576167617</v>
+      </c>
+      <c r="E2487" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2487" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G2487" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2487" s="3"/>
+      <c r="I2487" s="3"/>
+      <c r="J2487" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2487" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2487" s="3" t="s">
+        <v>3055</v>
+      </c>
+      <c r="M2487" s="3"/>
+    </row>
+    <row r="2488" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2488" s="3" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B2488" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2488" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2488" s="3">
+        <v>5576213183</v>
+      </c>
+      <c r="E2488" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2488" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="G2488" s="3"/>
+      <c r="H2488" s="3"/>
+      <c r="I2488" s="3"/>
+      <c r="J2488" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2488" s="3"/>
+      <c r="L2488" s="3"/>
+      <c r="M2488" s="3"/>
+    </row>
+    <row r="2489" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2489" s="3" t="s">
+        <v>3057</v>
+      </c>
+      <c r="B2489" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2489" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2489" s="3">
+        <v>5576346015</v>
+      </c>
+      <c r="E2489" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2489" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G2489" s="3"/>
+      <c r="H2489" s="3"/>
+      <c r="I2489" s="3"/>
+      <c r="J2489" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2489" s="3"/>
+      <c r="L2489" s="3"/>
+      <c r="M2489" s="3"/>
+    </row>
+    <row r="2490" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2490" s="3" t="s">
+        <v>3058</v>
+      </c>
+      <c r="B2490" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2490" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2490" s="3">
+        <v>5576403116</v>
+      </c>
+      <c r="E2490" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2490" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G2490" s="3"/>
+      <c r="H2490" s="3"/>
+      <c r="I2490" s="3"/>
+      <c r="J2490" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2490" s="3"/>
+      <c r="L2490" s="3"/>
+      <c r="M2490" s="3"/>
+    </row>
+    <row r="2491" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2491" s="3" t="s">
+        <v>3059</v>
+      </c>
+      <c r="B2491" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2491" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2491" s="3">
+        <v>5576417980</v>
+      </c>
+      <c r="E2491" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2491" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G2491" s="3"/>
+      <c r="H2491" s="3"/>
+      <c r="I2491" s="3"/>
+      <c r="J2491" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2491" s="3"/>
+      <c r="L2491" s="3"/>
+      <c r="M2491" s="3"/>
+    </row>
+    <row r="2492" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2492" s="3" t="s">
+        <v>3060</v>
+      </c>
+      <c r="B2492" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2492" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2492" s="3">
+        <v>5576439779</v>
+      </c>
+      <c r="E2492" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2492" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G2492" s="3"/>
+      <c r="H2492" s="3"/>
+      <c r="I2492" s="3"/>
+      <c r="J2492" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2492" s="3"/>
+      <c r="L2492" s="3"/>
+      <c r="M2492" s="3"/>
+    </row>
+    <row r="2493" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2493" s="3" t="s">
+        <v>3061</v>
+      </c>
+      <c r="B2493" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2493" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2493" s="3">
+        <v>5576647522</v>
+      </c>
+      <c r="E2493" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2493" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="G2493" s="3"/>
+      <c r="H2493" s="3"/>
+      <c r="I2493" s="3"/>
+      <c r="J2493" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2493" s="3"/>
+      <c r="L2493" s="3"/>
+      <c r="M2493" s="3"/>
+    </row>
+    <row r="2494" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2494" s="3" t="s">
+        <v>3062</v>
+      </c>
+      <c r="B2494" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2494" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2494" s="3">
+        <v>5576863461</v>
+      </c>
+      <c r="E2494" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2494" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G2494" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2494" s="3"/>
+      <c r="I2494" s="3"/>
+      <c r="J2494" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2494" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2494" s="3" t="s">
+        <v>3055</v>
+      </c>
+      <c r="M2494" s="3"/>
+    </row>
+    <row r="2495" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2495" s="3" t="s">
+        <v>3063</v>
+      </c>
+      <c r="B2495" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2495" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2495" s="3">
+        <v>5576887571</v>
+      </c>
+      <c r="E2495" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2495" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="G2495" s="3"/>
+      <c r="H2495" s="3"/>
+      <c r="I2495" s="3"/>
+      <c r="J2495" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2495" s="3"/>
+      <c r="L2495" s="3"/>
+      <c r="M2495" s="3"/>
+    </row>
+    <row r="2496" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2496" s="3" t="s">
+        <v>3064</v>
+      </c>
+      <c r="B2496" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2496" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2496" s="3">
+        <v>5576894886</v>
+      </c>
+      <c r="E2496" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2496" s="3" t="s">
+        <v>3065</v>
+      </c>
+      <c r="G2496" s="3"/>
+      <c r="H2496" s="3"/>
+      <c r="I2496" s="3"/>
+      <c r="J2496" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2496" s="3"/>
+      <c r="L2496" s="3"/>
+      <c r="M2496" s="3"/>
+    </row>
+    <row r="2497" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2497" s="3" t="s">
+        <v>3066</v>
+      </c>
+      <c r="B2497" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2497" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2497" s="3">
+        <v>5577138583</v>
+      </c>
+      <c r="E2497" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2497" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="G2497" s="3"/>
+      <c r="H2497" s="3"/>
+      <c r="I2497" s="3"/>
+      <c r="J2497" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2497" s="3"/>
+      <c r="L2497" s="3"/>
+      <c r="M2497" s="3"/>
+    </row>
+    <row r="2498" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2498" s="3" t="s">
+        <v>3067</v>
+      </c>
+      <c r="B2498" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2498" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2498" s="3">
+        <v>5577188046</v>
+      </c>
+      <c r="E2498" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2498" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2498" s="3"/>
+      <c r="H2498" s="3"/>
+      <c r="I2498" s="3"/>
+      <c r="J2498" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2498" s="3"/>
+      <c r="L2498" s="3"/>
+      <c r="M2498" s="3"/>
+    </row>
+    <row r="2499" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2499" s="3" t="s">
+        <v>3068</v>
+      </c>
+      <c r="B2499" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2499" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2499" s="3">
+        <v>5577341111</v>
+      </c>
+      <c r="E2499" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2499" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2499" s="3"/>
+      <c r="H2499" s="3"/>
+      <c r="I2499" s="3"/>
+      <c r="J2499" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2499" s="3"/>
+      <c r="L2499" s="3"/>
+      <c r="M2499" s="3"/>
+    </row>
+    <row r="2500" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2500" s="3" t="s">
+        <v>3069</v>
+      </c>
+      <c r="B2500" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2500" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2500" s="3">
+        <v>5577360289</v>
+      </c>
+      <c r="E2500" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2500" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="G2500" s="3"/>
+      <c r="H2500" s="3"/>
+      <c r="I2500" s="3"/>
+      <c r="J2500" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2500" s="3"/>
+      <c r="L2500" s="3"/>
+      <c r="M2500" s="3"/>
+    </row>
+    <row r="2501" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2501" s="3" t="s">
+        <v>3070</v>
+      </c>
+      <c r="B2501" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2501" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2501" s="3">
+        <v>5577362291</v>
+      </c>
+      <c r="E2501" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2501" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2501" s="3"/>
+      <c r="H2501" s="3"/>
+      <c r="I2501" s="3"/>
+      <c r="J2501" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2501" s="3"/>
+      <c r="L2501" s="3"/>
+      <c r="M2501" s="3"/>
+    </row>
+    <row r="2502" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2502" s="3" t="s">
+        <v>3071</v>
+      </c>
+      <c r="B2502" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2502" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2502" s="3">
+        <v>5577370889</v>
+      </c>
+      <c r="E2502" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2502" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2502" s="3"/>
+      <c r="H2502" s="3"/>
+      <c r="I2502" s="3"/>
+      <c r="J2502" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2502" s="3"/>
+      <c r="L2502" s="3"/>
+      <c r="M2502" s="3"/>
+    </row>
+    <row r="2503" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2503" s="3" t="s">
+        <v>3072</v>
+      </c>
+      <c r="B2503" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2503" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2503" s="3">
+        <v>5577422962</v>
+      </c>
+      <c r="E2503" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2503" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G2503" s="3"/>
+      <c r="H2503" s="3"/>
+      <c r="I2503" s="3"/>
+      <c r="J2503" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2503" s="3"/>
+      <c r="L2503" s="3"/>
+      <c r="M2503" s="3"/>
+    </row>
+    <row r="2504" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2504" s="3" t="s">
+        <v>3073</v>
+      </c>
+      <c r="B2504" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2504" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2504" s="3">
+        <v>5577641494</v>
+      </c>
+      <c r="E2504" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2504" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="G2504" s="3"/>
+      <c r="H2504" s="3"/>
+      <c r="I2504" s="3"/>
+      <c r="J2504" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2504" s="3"/>
+      <c r="L2504" s="3"/>
+      <c r="M2504" s="3"/>
+    </row>
+    <row r="2505" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2505" s="3" t="s">
+        <v>3074</v>
+      </c>
+      <c r="B2505" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2505" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2505" s="3">
+        <v>5577705693</v>
+      </c>
+      <c r="E2505" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2505" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G2505" s="3"/>
+      <c r="H2505" s="3"/>
+      <c r="I2505" s="3"/>
+      <c r="J2505" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2505" s="3"/>
+      <c r="L2505" s="3"/>
+      <c r="M2505" s="3"/>
+    </row>
+    <row r="2506" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2506" s="3" t="s">
+        <v>3075</v>
+      </c>
+      <c r="B2506" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2506" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2506" s="3">
+        <v>5577742018</v>
+      </c>
+      <c r="E2506" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2506" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G2506" s="3"/>
+      <c r="H2506" s="3"/>
+      <c r="I2506" s="3"/>
+      <c r="J2506" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2506" s="3"/>
+      <c r="L2506" s="3"/>
+      <c r="M2506" s="3"/>
+    </row>
+    <row r="2507" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2507" s="3" t="s">
+        <v>3075</v>
+      </c>
+      <c r="B2507" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2507" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2507" s="3">
+        <v>5577750675</v>
+      </c>
+      <c r="E2507" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2507" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G2507" s="3"/>
+      <c r="H2507" s="3"/>
+      <c r="I2507" s="3"/>
+      <c r="J2507" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2507" s="3"/>
+      <c r="L2507" s="3"/>
+      <c r="M2507" s="3"/>
+    </row>
+    <row r="2508" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2508" s="3" t="s">
+        <v>3076</v>
+      </c>
+      <c r="B2508" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2508" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2508" s="3">
+        <v>5577775802</v>
+      </c>
+      <c r="E2508" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2508" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="G2508" s="3"/>
+      <c r="H2508" s="3"/>
+      <c r="I2508" s="3"/>
+      <c r="J2508" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2508" s="3"/>
+      <c r="L2508" s="3"/>
+      <c r="M2508" s="3"/>
+    </row>
+    <row r="2509" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2509" s="3" t="s">
+        <v>3076</v>
+      </c>
+      <c r="B2509" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2509" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2509" s="3">
+        <v>5577777688</v>
+      </c>
+      <c r="E2509" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2509" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G2509" s="3"/>
+      <c r="H2509" s="3"/>
+      <c r="I2509" s="3"/>
+      <c r="J2509" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2509" s="3"/>
+      <c r="L2509" s="3"/>
+      <c r="M2509" s="3"/>
+    </row>
+    <row r="2510" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2510" s="3" t="s">
+        <v>3077</v>
+      </c>
+      <c r="B2510" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2510" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2510" s="3">
+        <v>5577859567</v>
+      </c>
+      <c r="E2510" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2510" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G2510" s="3"/>
+      <c r="H2510" s="3"/>
+      <c r="I2510" s="3"/>
+      <c r="J2510" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2510" s="3"/>
+      <c r="L2510" s="3"/>
+      <c r="M2510" s="3"/>
+    </row>
+    <row r="2511" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2511" s="3" t="s">
+        <v>3078</v>
+      </c>
+      <c r="B2511" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2511" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2511" s="3">
+        <v>5577877976</v>
+      </c>
+      <c r="E2511" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2511" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="G2511" s="3"/>
+      <c r="H2511" s="3"/>
+      <c r="I2511" s="3"/>
+      <c r="J2511" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2511" s="3"/>
+      <c r="L2511" s="3"/>
+      <c r="M2511" s="3"/>
+    </row>
+    <row r="2512" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2512" s="3" t="s">
+        <v>3079</v>
+      </c>
+      <c r="B2512" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2512" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2512" s="3">
+        <v>5578342397</v>
+      </c>
+      <c r="E2512" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2512" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="G2512" s="3"/>
+      <c r="H2512" s="3"/>
+      <c r="I2512" s="3"/>
+      <c r="J2512" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2512" s="3"/>
+      <c r="L2512" s="3"/>
+      <c r="M2512" s="3"/>
+    </row>
+    <row r="2513" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2513" s="3" t="s">
+        <v>3080</v>
+      </c>
+      <c r="B2513" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2513" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2513" s="3">
+        <v>5578427894</v>
+      </c>
+      <c r="E2513" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2513" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G2513" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2513" s="3"/>
+      <c r="I2513" s="3"/>
+      <c r="J2513" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2513" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2513" s="3" t="s">
+        <v>3055</v>
+      </c>
+      <c r="M2513" s="3"/>
+    </row>
+    <row r="2514" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2514" s="3" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B2514" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2514" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2514" s="3">
+        <v>5578465366</v>
+      </c>
+      <c r="E2514" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2514" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="G2514" s="3"/>
+      <c r="H2514" s="3"/>
+      <c r="I2514" s="3"/>
+      <c r="J2514" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2514" s="3"/>
+      <c r="L2514" s="3"/>
+      <c r="M2514" s="3"/>
+    </row>
+    <row r="2515" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2515" s="3" t="s">
+        <v>3082</v>
+      </c>
+      <c r="B2515" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2515" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2515" s="3">
+        <v>5578558774</v>
+      </c>
+      <c r="E2515" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2515" s="3" t="s">
+        <v>2377</v>
+      </c>
+      <c r="G2515" s="3"/>
+      <c r="H2515" s="3"/>
+      <c r="I2515" s="3"/>
+      <c r="J2515" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2515" s="3"/>
+      <c r="L2515" s="3"/>
+      <c r="M2515" s="3"/>
+    </row>
+    <row r="2516" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2516" s="3" t="s">
+        <v>3083</v>
+      </c>
+      <c r="B2516" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2516" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2516" s="3">
+        <v>5578601595</v>
+      </c>
+      <c r="E2516" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2516" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="G2516" s="3"/>
+      <c r="H2516" s="3"/>
+      <c r="I2516" s="3"/>
+      <c r="J2516" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2516" s="3"/>
+      <c r="L2516" s="3"/>
+      <c r="M2516" s="3"/>
+    </row>
+    <row r="2517" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2517" s="3" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B2517" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2517" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2517" s="3">
+        <v>5578658214</v>
+      </c>
+      <c r="E2517" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2517" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="G2517" s="3"/>
+      <c r="H2517" s="3"/>
+      <c r="I2517" s="3"/>
+      <c r="J2517" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2517" s="3"/>
+      <c r="L2517" s="3"/>
+      <c r="M2517" s="3"/>
+    </row>
+    <row r="2518" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2518" s="3" t="s">
+        <v>3085</v>
+      </c>
+      <c r="B2518" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2518" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2518" s="3">
+        <v>5578668507</v>
+      </c>
+      <c r="E2518" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2518" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G2518" s="3"/>
+      <c r="H2518" s="3"/>
+      <c r="I2518" s="3"/>
+      <c r="J2518" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2518" s="3"/>
+      <c r="L2518" s="3"/>
+      <c r="M2518" s="3"/>
+    </row>
+    <row r="2519" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2519" s="3" t="s">
+        <v>3086</v>
+      </c>
+      <c r="B2519" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2519" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2519" s="3">
+        <v>5578701965</v>
+      </c>
+      <c r="E2519" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F2519" s="3" t="s">
+        <v>1675</v>
+      </c>
+      <c r="G2519" s="3"/>
+      <c r="H2519" s="3">
+        <v>53</v>
+      </c>
+      <c r="I2519" s="3">
+        <v>40</v>
+      </c>
+      <c r="J2519" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2519" s="3"/>
+      <c r="L2519" s="3"/>
+      <c r="M2519" s="3"/>
+    </row>
+    <row r="2520" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2520" s="3" t="s">
+        <v>3087</v>
+      </c>
+      <c r="B2520" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2520" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2520" s="3">
+        <v>5582239175</v>
+      </c>
+      <c r="E2520" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2520" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2520" s="3"/>
+      <c r="H2520" s="3"/>
+      <c r="I2520" s="3"/>
+      <c r="J2520" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2520" s="3"/>
+      <c r="L2520" s="3"/>
+      <c r="M2520" s="3"/>
+    </row>
+    <row r="2521" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2521" s="3" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B2521" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2521" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2521" s="3">
+        <v>5582248866</v>
+      </c>
+      <c r="E2521" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2521" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2521" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2521" s="3"/>
+      <c r="I2521" s="3"/>
+      <c r="J2521" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2521" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2521" s="3" t="s">
+        <v>3089</v>
+      </c>
+      <c r="M2521" s="3"/>
+    </row>
+    <row r="2522" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2522" s="3" t="s">
+        <v>3090</v>
+      </c>
+      <c r="B2522" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2522" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2522" s="3">
+        <v>5582326113</v>
+      </c>
+      <c r="E2522" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2522" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2522" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2522" s="3"/>
+      <c r="I2522" s="3"/>
+      <c r="J2522" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2522" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2522" s="3" t="s">
+        <v>3089</v>
+      </c>
+      <c r="M2522" s="3"/>
+    </row>
+    <row r="2523" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2523" s="3" t="s">
+        <v>3091</v>
+      </c>
+      <c r="B2523" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2523" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2523" s="3">
+        <v>5582339637</v>
+      </c>
+      <c r="E2523" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F2523" s="3" t="s">
+        <v>3092</v>
+      </c>
+      <c r="G2523" s="3"/>
+      <c r="H2523" s="3"/>
+      <c r="I2523" s="3"/>
+      <c r="J2523" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2523" s="3"/>
+      <c r="L2523" s="3"/>
+      <c r="M2523" s="3"/>
+    </row>
+    <row r="2524" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2524" s="3" t="s">
+        <v>3093</v>
+      </c>
+      <c r="B2524" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2524" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2524" s="3">
+        <v>5582339640</v>
+      </c>
+      <c r="E2524" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F2524" s="3" t="s">
+        <v>3094</v>
+      </c>
+      <c r="G2524" s="3"/>
+      <c r="H2524" s="3"/>
+      <c r="I2524" s="3"/>
+      <c r="J2524" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2524" s="3"/>
+      <c r="L2524" s="3"/>
+      <c r="M2524" s="3"/>
+    </row>
+    <row r="2525" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2525" s="3" t="s">
+        <v>3095</v>
+      </c>
+      <c r="B2525" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2525" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2525" s="3">
+        <v>5582433885</v>
+      </c>
+      <c r="E2525" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="F2525" s="3" t="s">
+        <v>1884</v>
+      </c>
+      <c r="G2525" s="3"/>
+      <c r="H2525" s="3"/>
+      <c r="I2525" s="3"/>
+      <c r="J2525" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2525" s="3"/>
+      <c r="L2525" s="3"/>
+      <c r="M2525" s="3"/>
+    </row>
+    <row r="2526" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2526" s="3" t="s">
+        <v>3096</v>
+      </c>
+      <c r="B2526" s="3"/>
+      <c r="C2526" s="3"/>
+      <c r="D2526" s="3">
+        <v>5582795297</v>
+      </c>
+      <c r="E2526" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2526" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G2526" s="3"/>
+      <c r="H2526" s="3"/>
+      <c r="I2526" s="3"/>
+      <c r="J2526" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2526" s="3"/>
+      <c r="L2526" s="3"/>
+      <c r="M2526" s="3"/>
+    </row>
+    <row r="2527" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2527" s="3" t="s">
+        <v>3097</v>
+      </c>
+      <c r="B2527" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2527" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2527" s="3">
+        <v>5582847440</v>
+      </c>
+      <c r="E2527" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2527" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G2527" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2527" s="3"/>
+      <c r="I2527" s="3"/>
+      <c r="J2527" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2527" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2527" s="3" t="s">
+        <v>3089</v>
+      </c>
+      <c r="M2527" s="3"/>
+    </row>
+    <row r="2528" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2528" s="3" t="s">
+        <v>3098</v>
+      </c>
+      <c r="B2528" s="3"/>
+      <c r="C2528" s="3"/>
+      <c r="D2528" s="3">
+        <v>5582969605</v>
+      </c>
+      <c r="E2528" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2528" s="3" t="s">
+        <v>1991</v>
+      </c>
+      <c r="G2528" s="3"/>
+      <c r="H2528" s="3"/>
+      <c r="I2528" s="3"/>
+      <c r="J2528" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2528" s="3"/>
+      <c r="L2528" s="3"/>
+      <c r="M2528" s="3"/>
+    </row>
+    <row r="2529" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2529" s="3" t="s">
+        <v>3099</v>
+      </c>
+      <c r="B2529" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2529" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2529" s="3">
+        <v>5583060577</v>
+      </c>
+      <c r="E2529" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2529" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="G2529" s="3"/>
+      <c r="H2529" s="3"/>
+      <c r="I2529" s="3"/>
+      <c r="J2529" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2529" s="3"/>
+      <c r="L2529" s="3"/>
+      <c r="M2529" s="3"/>
+    </row>
+    <row r="2530" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2530" s="3" t="s">
+        <v>3100</v>
+      </c>
+      <c r="B2530" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2530" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2530" s="3">
+        <v>5583161980</v>
+      </c>
+      <c r="E2530" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2530" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G2530" s="3"/>
+      <c r="H2530" s="3"/>
+      <c r="I2530" s="3"/>
+      <c r="J2530" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2530" s="3"/>
+      <c r="L2530" s="3"/>
+      <c r="M2530" s="3"/>
+    </row>
+    <row r="2531" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2531" s="3" t="s">
+        <v>3101</v>
+      </c>
+      <c r="B2531" s="3"/>
+      <c r="C2531" s="3"/>
+      <c r="D2531" s="3">
+        <v>5583203812</v>
+      </c>
+      <c r="E2531" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2531" s="3" t="s">
+        <v>2670</v>
+      </c>
+      <c r="G2531" s="3"/>
+      <c r="H2531" s="3"/>
+      <c r="I2531" s="3"/>
+      <c r="J2531" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2531" s="3"/>
+      <c r="L2531" s="3"/>
+      <c r="M2531" s="3"/>
+    </row>
+    <row r="2532" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2532" s="3" t="s">
+        <v>3102</v>
+      </c>
+      <c r="B2532" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2532" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2532" s="3">
+        <v>5583375439</v>
+      </c>
+      <c r="E2532" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2532" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="G2532" s="3"/>
+      <c r="H2532" s="3"/>
+      <c r="I2532" s="3"/>
+      <c r="J2532" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2532" s="3"/>
+      <c r="L2532" s="3"/>
+      <c r="M2532" s="3"/>
+    </row>
+    <row r="2533" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2533" s="3" t="s">
+        <v>3103</v>
+      </c>
+      <c r="B2533" s="3"/>
+      <c r="C2533" s="3"/>
+      <c r="D2533" s="3">
+        <v>5583519642</v>
+      </c>
+      <c r="E2533" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2533" s="3" t="s">
+        <v>2670</v>
+      </c>
+      <c r="G2533" s="3"/>
+      <c r="H2533" s="3"/>
+      <c r="I2533" s="3"/>
+      <c r="J2533" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2533" s="3"/>
+      <c r="L2533" s="3"/>
+      <c r="M2533" s="3"/>
+    </row>
+    <row r="2534" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2534" s="3" t="s">
+        <v>3104</v>
+      </c>
+      <c r="B2534" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2534" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2534" s="3">
+        <v>5583624469</v>
+      </c>
+      <c r="E2534" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2534" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G2534" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2534" s="3"/>
+      <c r="I2534" s="3"/>
+      <c r="J2534" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2534" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2534" s="3" t="s">
+        <v>3089</v>
+      </c>
+      <c r="M2534" s="3"/>
+    </row>
+    <row r="2535" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2535" s="3" t="s">
+        <v>3105</v>
+      </c>
+      <c r="B2535" s="3"/>
+      <c r="C2535" s="3"/>
+      <c r="D2535" s="3">
+        <v>5583602997</v>
+      </c>
+      <c r="E2535" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2535" s="3" t="s">
+        <v>3106</v>
+      </c>
+      <c r="G2535" s="3"/>
+      <c r="H2535" s="3"/>
+      <c r="I2535" s="3"/>
+      <c r="J2535" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2535" s="3"/>
+      <c r="L2535" s="3"/>
+      <c r="M2535" s="3"/>
+    </row>
+    <row r="2536" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2536" s="3" t="s">
+        <v>3107</v>
+      </c>
+      <c r="B2536" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2536" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2536" s="3">
+        <v>5583663395</v>
+      </c>
+      <c r="E2536" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2536" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G2536" s="3"/>
+      <c r="H2536" s="3"/>
+      <c r="I2536" s="3"/>
+      <c r="J2536" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2536" s="3"/>
+      <c r="L2536" s="3"/>
+      <c r="M2536" s="3"/>
+    </row>
+    <row r="2537" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2537" s="3" t="s">
+        <v>3108</v>
+      </c>
+      <c r="B2537" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2537" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2537" s="3">
+        <v>5583815632</v>
+      </c>
+      <c r="E2537" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2537" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G2537" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2537" s="3"/>
+      <c r="I2537" s="3"/>
+      <c r="J2537" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2537" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2537" s="3" t="s">
+        <v>3089</v>
+      </c>
+      <c r="M2537" s="3"/>
+    </row>
+    <row r="2538" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2538" s="3" t="s">
+        <v>3108</v>
+      </c>
+      <c r="B2538" s="3"/>
+      <c r="C2538" s="3"/>
+      <c r="D2538" s="3">
+        <v>5583812810</v>
+      </c>
+      <c r="E2538" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2538" s="3" t="s">
+        <v>3109</v>
+      </c>
+      <c r="G2538" s="3"/>
+      <c r="H2538" s="3"/>
+      <c r="I2538" s="3"/>
+      <c r="J2538" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2538" s="3"/>
+      <c r="L2538" s="3"/>
+      <c r="M2538" s="3"/>
+    </row>
+    <row r="2539" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2539" s="3" t="s">
+        <v>3110</v>
+      </c>
+      <c r="B2539" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2539" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2539" s="3">
+        <v>5584124984</v>
+      </c>
+      <c r="E2539" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2539" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="G2539" s="3"/>
+      <c r="H2539" s="3"/>
+      <c r="I2539" s="3"/>
+      <c r="J2539" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2539" s="3"/>
+      <c r="L2539" s="3"/>
+      <c r="M2539" s="3"/>
+    </row>
+    <row r="2540" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2540" s="3" t="s">
+        <v>3111</v>
+      </c>
+      <c r="B2540" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2540" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2540" s="3">
+        <v>5584410664</v>
+      </c>
+      <c r="E2540" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2540" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="G2540" s="3"/>
+      <c r="H2540" s="3"/>
+      <c r="I2540" s="3"/>
+      <c r="J2540" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2540" s="3"/>
+      <c r="L2540" s="3"/>
+      <c r="M2540" s="3"/>
+    </row>
+    <row r="2541" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2541" s="3" t="s">
+        <v>3112</v>
+      </c>
+      <c r="B2541" s="3"/>
+      <c r="C2541" s="3"/>
+      <c r="D2541" s="3">
+        <v>5584427890</v>
+      </c>
+      <c r="E2541" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2541" s="3" t="s">
+        <v>3113</v>
+      </c>
+      <c r="G2541" s="3"/>
+      <c r="H2541" s="3"/>
+      <c r="I2541" s="3"/>
+      <c r="J2541" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2541" s="3"/>
+      <c r="L2541" s="3"/>
+      <c r="M2541" s="3"/>
+    </row>
+    <row r="2542" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2542" s="3" t="s">
+        <v>3114</v>
+      </c>
+      <c r="B2542" s="3"/>
+      <c r="C2542" s="3"/>
+      <c r="D2542" s="3">
+        <v>5585052610</v>
+      </c>
+      <c r="E2542" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="F2542" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2542" s="3"/>
+      <c r="H2542" s="3"/>
+      <c r="I2542" s="3"/>
+      <c r="J2542" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2542" s="3"/>
+      <c r="L2542" s="3"/>
+      <c r="M2542" s="3"/>
+    </row>
+    <row r="2543" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2543" s="3" t="s">
+        <v>3115</v>
+      </c>
+      <c r="B2543" s="3"/>
+      <c r="C2543" s="3"/>
+      <c r="D2543" s="3">
+        <v>5585080813</v>
+      </c>
+      <c r="E2543" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2543" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2543" s="3"/>
+      <c r="H2543" s="3"/>
+      <c r="I2543" s="3"/>
+      <c r="J2543" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2543" s="3"/>
+      <c r="L2543" s="3"/>
+      <c r="M2543" s="3"/>
+    </row>
+    <row r="2544" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2544" s="3" t="s">
+        <v>3116</v>
+      </c>
+      <c r="B2544" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2544" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2544" s="3">
+        <v>5585473745</v>
+      </c>
+      <c r="E2544" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2544" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G2544" s="3"/>
+      <c r="H2544" s="3"/>
+      <c r="I2544" s="3"/>
+      <c r="J2544" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2544" s="3"/>
+      <c r="L2544" s="3"/>
+      <c r="M2544" s="3"/>
+    </row>
+    <row r="2545" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2545" s="3" t="s">
+        <v>3117</v>
+      </c>
+      <c r="B2545" s="3" t="s">
+        <v>3054</v>
+      </c>
+      <c r="C2545" s="3"/>
+      <c r="D2545" s="3">
+        <v>5585415328</v>
+      </c>
+      <c r="E2545" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2545" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="G2545" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2545" s="3"/>
+      <c r="I2545" s="3"/>
+      <c r="J2545" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2545" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2545" s="3" t="s">
+        <v>3118</v>
+      </c>
+      <c r="M2545" s="3"/>
+    </row>
+    <row r="2546" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2546" s="3" t="s">
+        <v>3119</v>
+      </c>
+      <c r="B2546" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2546" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2546" s="3">
+        <v>5585774227</v>
+      </c>
+      <c r="E2546" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2546" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="G2546" s="3"/>
+      <c r="H2546" s="3"/>
+      <c r="I2546" s="3"/>
+      <c r="J2546" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2546" s="3"/>
+      <c r="L2546" s="3"/>
+      <c r="M2546" s="3"/>
+    </row>
+    <row r="2547" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2547" s="3" t="s">
+        <v>3120</v>
+      </c>
+      <c r="B2547" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2547" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2547" s="3">
+        <v>5589022722</v>
+      </c>
+      <c r="E2547" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2547" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2547" s="3"/>
+      <c r="H2547" s="3"/>
+      <c r="I2547" s="3"/>
+      <c r="J2547" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2547" s="3"/>
+      <c r="L2547" s="3"/>
+      <c r="M2547" s="3"/>
+    </row>
+    <row r="2548" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2548" s="3" t="s">
+        <v>3121</v>
+      </c>
+      <c r="B2548" s="3"/>
+      <c r="C2548" s="3"/>
+      <c r="D2548" s="3">
+        <v>5589188950</v>
+      </c>
+      <c r="E2548" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2548" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2548" s="3"/>
+      <c r="H2548" s="3"/>
+      <c r="I2548" s="3"/>
+      <c r="J2548" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2548" s="3"/>
+      <c r="L2548" s="3"/>
+      <c r="M2548" s="3"/>
+    </row>
+    <row r="2549" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2549" s="3" t="s">
+        <v>3122</v>
+      </c>
+      <c r="B2549" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2549" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2549" s="3">
+        <v>5589161656</v>
+      </c>
+      <c r="E2549" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2549" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2549" s="3"/>
+      <c r="H2549" s="3"/>
+      <c r="I2549" s="3"/>
+      <c r="J2549" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2549" s="3"/>
+      <c r="L2549" s="3"/>
+      <c r="M2549" s="3"/>
+    </row>
+    <row r="2550" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2550" s="3" t="s">
+        <v>3123</v>
+      </c>
+      <c r="B2550" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2550" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2550" s="3">
+        <v>5589236211</v>
+      </c>
+      <c r="E2550" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2550" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2550" s="3"/>
+      <c r="H2550" s="3"/>
+      <c r="I2550" s="3"/>
+      <c r="J2550" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2550" s="3"/>
+      <c r="L2550" s="3"/>
+      <c r="M2550" s="3"/>
+    </row>
+    <row r="2551" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2551" s="3" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B2551" s="3"/>
+      <c r="C2551" s="3"/>
+      <c r="D2551" s="3">
+        <v>5589247007</v>
+      </c>
+      <c r="E2551" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2551" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G2551" s="3"/>
+      <c r="H2551" s="3"/>
+      <c r="I2551" s="3"/>
+      <c r="J2551" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2551" s="3"/>
+      <c r="L2551" s="3"/>
+      <c r="M2551" s="3"/>
+    </row>
+    <row r="2552" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2552" s="3" t="s">
+        <v>3125</v>
+      </c>
+      <c r="B2552" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2552" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2552" s="3">
+        <v>5589546382</v>
+      </c>
+      <c r="E2552" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2552" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2552" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2552" s="3"/>
+      <c r="I2552" s="3"/>
+      <c r="J2552" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2552" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2552" s="3" t="s">
+        <v>3126</v>
+      </c>
+      <c r="M2552" s="3"/>
+    </row>
+    <row r="2553" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2553" s="3" t="s">
+        <v>3127</v>
+      </c>
+      <c r="B2553" s="3"/>
+      <c r="C2553" s="3"/>
+      <c r="D2553" s="3">
+        <v>5589658609</v>
+      </c>
+      <c r="E2553" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2553" s="3" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G2553" s="3"/>
+      <c r="H2553" s="3"/>
+      <c r="I2553" s="3"/>
+      <c r="J2553" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2553" s="3"/>
+      <c r="L2553" s="3"/>
+      <c r="M2553" s="3"/>
+    </row>
+    <row r="2554" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2554" s="3" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B2554" s="3"/>
+      <c r="C2554" s="3"/>
+      <c r="D2554" s="3">
+        <v>5589671445</v>
+      </c>
+      <c r="E2554" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2554" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2554" s="3"/>
+      <c r="H2554" s="3"/>
+      <c r="I2554" s="3"/>
+      <c r="J2554" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2554" s="3"/>
+      <c r="L2554" s="3"/>
+      <c r="M2554" s="3"/>
+    </row>
+    <row r="2555" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2555" s="3" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B2555" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2555" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2555" s="3">
+        <v>5589744911</v>
+      </c>
+      <c r="E2555" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2555" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2555" s="3"/>
+      <c r="H2555" s="3"/>
+      <c r="I2555" s="3"/>
+      <c r="J2555" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2555" s="3"/>
+      <c r="L2555" s="3"/>
+      <c r="M2555" s="3"/>
+    </row>
+    <row r="2556" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2556" s="3" t="s">
+        <v>3130</v>
+      </c>
+      <c r="B2556" s="3"/>
+      <c r="C2556" s="3"/>
+      <c r="D2556" s="3">
+        <v>5589818754</v>
+      </c>
+      <c r="E2556" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2556" s="3" t="s">
+        <v>1847</v>
+      </c>
+      <c r="G2556" s="3"/>
+      <c r="H2556" s="3"/>
+      <c r="I2556" s="3"/>
+      <c r="J2556" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2556" s="3"/>
+      <c r="L2556" s="3"/>
+      <c r="M2556" s="3"/>
+    </row>
+    <row r="2557" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2557" s="3" t="s">
+        <v>3131</v>
+      </c>
+      <c r="B2557" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2557" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2557" s="3">
+        <v>5589882074</v>
+      </c>
+      <c r="E2557" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2557" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G2557" s="3"/>
+      <c r="H2557" s="3"/>
+      <c r="I2557" s="3"/>
+      <c r="J2557" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2557" s="3"/>
+      <c r="L2557" s="3"/>
+      <c r="M2557" s="3"/>
+    </row>
+    <row r="2558" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2558" s="3" t="s">
+        <v>3132</v>
+      </c>
+      <c r="B2558" s="3"/>
+      <c r="C2558" s="3"/>
+      <c r="D2558" s="3">
+        <v>5589888848</v>
+      </c>
+      <c r="E2558" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2558" s="3" t="s">
+        <v>1847</v>
+      </c>
+      <c r="G2558" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2558" s="3"/>
+      <c r="I2558" s="3"/>
+      <c r="J2558" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2558" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2558" s="3" t="s">
+        <v>3126</v>
+      </c>
+      <c r="M2558" s="3"/>
+    </row>
+    <row r="2559" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2559" s="3" t="s">
+        <v>3133</v>
+      </c>
+      <c r="B2559" s="3"/>
+      <c r="C2559" s="3"/>
+      <c r="D2559" s="3">
+        <v>5589990933</v>
+      </c>
+      <c r="E2559" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2559" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2559" s="3"/>
+      <c r="H2559" s="3"/>
+      <c r="I2559" s="3"/>
+      <c r="J2559" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2559" s="3"/>
+      <c r="L2559" s="3"/>
+      <c r="M2559" s="3"/>
+    </row>
+    <row r="2560" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2560" s="3" t="s">
+        <v>3134</v>
+      </c>
+      <c r="B2560" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2560" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2560" s="3">
+        <v>5590021379</v>
+      </c>
+      <c r="E2560" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2560" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G2560" s="3"/>
+      <c r="H2560" s="3"/>
+      <c r="I2560" s="3"/>
+      <c r="J2560" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2560" s="3"/>
+      <c r="L2560" s="3"/>
+      <c r="M2560" s="3"/>
+    </row>
+    <row r="2561" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2561" s="3" t="s">
+        <v>3135</v>
+      </c>
+      <c r="B2561" s="3"/>
+      <c r="C2561" s="3"/>
+      <c r="D2561" s="3">
+        <v>5590103968</v>
+      </c>
+      <c r="E2561" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2561" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="G2561" s="3"/>
+      <c r="H2561" s="3"/>
+      <c r="I2561" s="3"/>
+      <c r="J2561" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2561" s="3"/>
+      <c r="L2561" s="3"/>
+      <c r="M2561" s="3"/>
+    </row>
+    <row r="2562" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2562" s="3" t="s">
+        <v>3136</v>
+      </c>
+      <c r="B2562" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2562" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2562" s="3">
+        <v>5590120202</v>
+      </c>
+      <c r="E2562" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2562" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G2562" s="3"/>
+      <c r="H2562" s="3"/>
+      <c r="I2562" s="3"/>
+      <c r="J2562" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2562" s="3"/>
+      <c r="L2562" s="3"/>
+      <c r="M2562" s="3"/>
+    </row>
+    <row r="2563" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2563" s="3" t="s">
+        <v>3137</v>
+      </c>
+      <c r="B2563" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2563" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2563" s="3">
+        <v>5590247219</v>
+      </c>
+      <c r="E2563" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2563" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G2563" s="3"/>
+      <c r="H2563" s="3"/>
+      <c r="I2563" s="3"/>
+      <c r="J2563" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2563" s="3"/>
+      <c r="L2563" s="3"/>
+      <c r="M2563" s="3"/>
+    </row>
+    <row r="2564" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2564" s="3" t="s">
+        <v>3138</v>
+      </c>
+      <c r="B2564" s="3"/>
+      <c r="C2564" s="3"/>
+      <c r="D2564" s="3">
+        <v>5590271315</v>
+      </c>
+      <c r="E2564" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2564" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2564" s="3"/>
+      <c r="H2564" s="3"/>
+      <c r="I2564" s="3"/>
+      <c r="J2564" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2564" s="3"/>
+      <c r="L2564" s="3"/>
+      <c r="M2564" s="3"/>
+    </row>
+    <row r="2565" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2565" s="3" t="s">
+        <v>3139</v>
+      </c>
+      <c r="B2565" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2565" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2565" s="3">
+        <v>5590403051</v>
+      </c>
+      <c r="E2565" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2565" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2565" s="3"/>
+      <c r="H2565" s="3"/>
+      <c r="I2565" s="3"/>
+      <c r="J2565" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2565" s="3"/>
+      <c r="L2565" s="3"/>
+      <c r="M2565" s="3"/>
+    </row>
+    <row r="2566" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2566" s="3" t="s">
+        <v>3140</v>
+      </c>
+      <c r="B2566" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2566" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2566" s="3">
+        <v>5590481131</v>
+      </c>
+      <c r="E2566" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2566" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="G2566" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2566" s="3"/>
+      <c r="I2566" s="3"/>
+      <c r="J2566" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2566" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2566" s="3" t="s">
+        <v>3126</v>
+      </c>
+      <c r="M2566" s="3"/>
+    </row>
+    <row r="2567" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2567" s="3" t="s">
+        <v>3141</v>
+      </c>
+      <c r="B2567" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2567" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2567" s="3">
+        <v>5590768672</v>
+      </c>
+      <c r="E2567" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2567" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2567" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2567" s="3"/>
+      <c r="I2567" s="3"/>
+      <c r="J2567" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2567" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2567" s="3" t="s">
+        <v>3126</v>
+      </c>
+      <c r="M2567" s="3"/>
+    </row>
+    <row r="2568" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2568" s="3" t="s">
+        <v>3142</v>
+      </c>
+      <c r="B2568" s="3"/>
+      <c r="C2568" s="3"/>
+      <c r="D2568" s="3">
+        <v>5590961194</v>
+      </c>
+      <c r="E2568" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2568" s="3" t="s">
+        <v>2251</v>
+      </c>
+      <c r="G2568" s="3"/>
+      <c r="H2568" s="3"/>
+      <c r="I2568" s="3"/>
+      <c r="J2568" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2568" s="3"/>
+      <c r="L2568" s="3"/>
+      <c r="M2568" s="3"/>
+    </row>
+    <row r="2569" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2569" s="3" t="s">
+        <v>3143</v>
+      </c>
+      <c r="B2569" s="3"/>
+      <c r="C2569" s="3"/>
+      <c r="D2569" s="3">
+        <v>5591118385</v>
+      </c>
+      <c r="E2569" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2569" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="G2569" s="3"/>
+      <c r="H2569" s="3"/>
+      <c r="I2569" s="3"/>
+      <c r="J2569" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2569" s="3"/>
+      <c r="L2569" s="3"/>
+      <c r="M2569" s="3"/>
+    </row>
+    <row r="2570" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2570" s="3" t="s">
+        <v>3144</v>
+      </c>
+      <c r="B2570" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2570" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2570" s="3">
+        <v>5591196144</v>
+      </c>
+      <c r="E2570" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2570" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2570" s="3"/>
+      <c r="H2570" s="3"/>
+      <c r="I2570" s="3"/>
+      <c r="J2570" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2570" s="3"/>
+      <c r="L2570" s="3"/>
+      <c r="M2570" s="3"/>
+    </row>
+    <row r="2571" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2571" s="3" t="s">
+        <v>3145</v>
+      </c>
+      <c r="B2571" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2571" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2571" s="3">
+        <v>5591281720</v>
+      </c>
+      <c r="E2571" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2571" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="G2571" s="3"/>
+      <c r="H2571" s="3"/>
+      <c r="I2571" s="3"/>
+      <c r="J2571" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2571" s="3"/>
+      <c r="L2571" s="3"/>
+      <c r="M2571" s="3"/>
+    </row>
+    <row r="2572" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2572" s="3" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B2572" s="3"/>
+      <c r="C2572" s="3"/>
+      <c r="D2572" s="3">
+        <v>5591320667</v>
+      </c>
+      <c r="E2572" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2572" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2572" s="3"/>
+      <c r="H2572" s="3"/>
+      <c r="I2572" s="3"/>
+      <c r="J2572" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2572" s="3"/>
+      <c r="L2572" s="3"/>
+      <c r="M2572" s="3"/>
+    </row>
+    <row r="2573" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2573" s="3" t="s">
+        <v>3147</v>
+      </c>
+      <c r="B2573" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2573" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2573" s="3">
+        <v>5591478312</v>
+      </c>
+      <c r="E2573" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2573" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2573" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2573" s="3"/>
+      <c r="I2573" s="3"/>
+      <c r="J2573" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2573" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2573" s="3" t="s">
+        <v>3126</v>
+      </c>
+      <c r="M2573" s="3"/>
+    </row>
+    <row r="2574" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2574" s="3" t="s">
+        <v>3148</v>
+      </c>
+      <c r="B2574" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2574" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2574" s="3">
+        <v>5591613925</v>
+      </c>
+      <c r="E2574" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2574" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2574" s="3"/>
+      <c r="H2574" s="3"/>
+      <c r="I2574" s="3"/>
+      <c r="J2574" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2574" s="3"/>
+      <c r="L2574" s="3"/>
+      <c r="M2574" s="3"/>
+    </row>
+    <row r="2575" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2575" s="3" t="s">
+        <v>3149</v>
+      </c>
+      <c r="B2575" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2575" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2575" s="3">
+        <v>5591671280</v>
+      </c>
+      <c r="E2575" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2575" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2575" s="3"/>
+      <c r="H2575" s="3"/>
+      <c r="I2575" s="3"/>
+      <c r="J2575" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2575" s="3"/>
+      <c r="L2575" s="3"/>
+      <c r="M2575" s="3"/>
+    </row>
+    <row r="2576" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2576" s="3" t="s">
+        <v>3150</v>
+      </c>
+      <c r="B2576" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2576" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2576" s="3">
+        <v>5592042213</v>
+      </c>
+      <c r="E2576" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="F2576" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2576" s="3"/>
+      <c r="H2576" s="3"/>
+      <c r="I2576" s="3"/>
+      <c r="J2576" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2576" s="3"/>
+      <c r="L2576" s="3"/>
+      <c r="M2576" s="3"/>
+    </row>
+    <row r="2577" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2577" s="3" t="s">
+        <v>3151</v>
+      </c>
+      <c r="B2577" s="3"/>
+      <c r="C2577" s="3"/>
+      <c r="D2577" s="3">
+        <v>5595857057</v>
+      </c>
+      <c r="E2577" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2577" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2577" s="3"/>
+      <c r="H2577" s="3"/>
+      <c r="I2577" s="3"/>
+      <c r="J2577" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2577" s="3"/>
+      <c r="L2577" s="3"/>
+      <c r="M2577" s="3"/>
+    </row>
+    <row r="2578" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2578" s="3" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B2578" s="3"/>
+      <c r="C2578" s="3"/>
+      <c r="D2578" s="3">
+        <v>5595872264</v>
+      </c>
+      <c r="E2578" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="F2578" s="3" t="s">
+        <v>3153</v>
+      </c>
+      <c r="G2578" s="3"/>
+      <c r="H2578" s="3"/>
+      <c r="I2578" s="3"/>
+      <c r="J2578" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2578" s="3"/>
+      <c r="L2578" s="3"/>
+      <c r="M2578" s="3"/>
+    </row>
+    <row r="2579" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2579" s="3" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B2579" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2579" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2579" s="3">
+        <v>5595876149</v>
+      </c>
+      <c r="E2579" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2579" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="G2579" s="3"/>
+      <c r="H2579" s="3"/>
+      <c r="I2579" s="3"/>
+      <c r="J2579" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2579" s="3"/>
+      <c r="L2579" s="3"/>
+      <c r="M2579" s="3"/>
+    </row>
+    <row r="2580" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2580" s="3" t="s">
+        <v>3154</v>
+      </c>
+      <c r="B2580" s="3"/>
+      <c r="C2580" s="3"/>
+      <c r="D2580" s="3">
+        <v>5595942985</v>
+      </c>
+      <c r="E2580" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2580" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G2580" s="3"/>
+      <c r="H2580" s="3"/>
+      <c r="I2580" s="3"/>
+      <c r="J2580" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2580" s="3"/>
+      <c r="L2580" s="3"/>
+      <c r="M2580" s="3"/>
+    </row>
+    <row r="2581" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2581" s="3" t="s">
+        <v>3155</v>
+      </c>
+      <c r="B2581" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2581" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2581" s="3">
+        <v>5596046250</v>
+      </c>
+      <c r="E2581" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2581" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G2581" s="3"/>
+      <c r="H2581" s="3"/>
+      <c r="I2581" s="3"/>
+      <c r="J2581" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2581" s="3"/>
+      <c r="L2581" s="3"/>
+      <c r="M2581" s="3"/>
+    </row>
+    <row r="2582" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2582" s="3" t="s">
+        <v>3156</v>
+      </c>
+      <c r="B2582" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2582" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2582" s="3">
+        <v>5596106170</v>
+      </c>
+      <c r="E2582" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2582" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="G2582" s="3"/>
+      <c r="H2582" s="3"/>
+      <c r="I2582" s="3"/>
+      <c r="J2582" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2582" s="3"/>
+      <c r="L2582" s="3"/>
+      <c r="M2582" s="3"/>
+    </row>
+    <row r="2583" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2583" s="3" t="s">
+        <v>3157</v>
+      </c>
+      <c r="B2583" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2583" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2583" s="3">
+        <v>5596161332</v>
+      </c>
+      <c r="E2583" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2583" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2583" s="3"/>
+      <c r="H2583" s="3"/>
+      <c r="I2583" s="3"/>
+      <c r="J2583" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2583" s="3"/>
+      <c r="L2583" s="3"/>
+      <c r="M2583" s="3"/>
+    </row>
+    <row r="2584" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2584" s="3" t="s">
+        <v>3158</v>
+      </c>
+      <c r="B2584" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2584" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2584" s="3">
+        <v>5596213114</v>
+      </c>
+      <c r="E2584" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2584" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="G2584" s="3"/>
+      <c r="H2584" s="3"/>
+      <c r="I2584" s="3"/>
+      <c r="J2584" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2584" s="3"/>
+      <c r="L2584" s="3"/>
+      <c r="M2584" s="3"/>
+    </row>
+    <row r="2585" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2585" s="3" t="s">
+        <v>3159</v>
+      </c>
+      <c r="B2585" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2585" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2585" s="3">
+        <v>5596252065</v>
+      </c>
+      <c r="E2585" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2585" s="3" t="s">
+        <v>2067</v>
+      </c>
+      <c r="G2585" s="3"/>
+      <c r="H2585" s="3"/>
+      <c r="I2585" s="3"/>
+      <c r="J2585" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2585" s="3"/>
+      <c r="L2585" s="3"/>
+      <c r="M2585" s="3"/>
+    </row>
+    <row r="2586" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2586" s="3" t="s">
+        <v>3160</v>
+      </c>
+      <c r="B2586" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2586" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2586" s="3">
+        <v>5596280337</v>
+      </c>
+      <c r="E2586" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2586" s="3" t="s">
+        <v>2067</v>
+      </c>
+      <c r="G2586" s="3"/>
+      <c r="H2586" s="3"/>
+      <c r="I2586" s="3"/>
+      <c r="J2586" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2586" s="3"/>
+      <c r="L2586" s="3"/>
+      <c r="M2586" s="3"/>
+    </row>
+    <row r="2587" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2587" s="3" t="s">
+        <v>3161</v>
+      </c>
+      <c r="B2587" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2587" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2587" s="3">
+        <v>5596370801</v>
+      </c>
+      <c r="E2587" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2587" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G2587" s="3"/>
+      <c r="H2587" s="3"/>
+      <c r="I2587" s="3"/>
+      <c r="J2587" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2587" s="3"/>
+      <c r="L2587" s="3"/>
+      <c r="M2587" s="3"/>
+    </row>
+    <row r="2588" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2588" s="3" t="s">
+        <v>3162</v>
+      </c>
+      <c r="B2588" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2588" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2588" s="3">
+        <v>5596543170</v>
+      </c>
+      <c r="E2588" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2588" s="3" t="s">
+        <v>2078</v>
+      </c>
+      <c r="G2588" s="3"/>
+      <c r="H2588" s="3"/>
+      <c r="I2588" s="3"/>
+      <c r="J2588" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2588" s="3"/>
+      <c r="L2588" s="3"/>
+      <c r="M2588" s="3"/>
+    </row>
+    <row r="2589" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2589" s="3" t="s">
+        <v>3163</v>
+      </c>
+      <c r="B2589" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2589" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2589" s="3">
+        <v>5596652876</v>
+      </c>
+      <c r="E2589" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2589" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G2589" s="3"/>
+      <c r="H2589" s="3"/>
+      <c r="I2589" s="3"/>
+      <c r="J2589" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2589" s="3"/>
+      <c r="L2589" s="3"/>
+      <c r="M2589" s="3"/>
+    </row>
+    <row r="2590" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2590" s="3" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B2590" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2590" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2590" s="3">
+        <v>5596680263</v>
+      </c>
+      <c r="E2590" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2590" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2590" s="3"/>
+      <c r="H2590" s="3"/>
+      <c r="I2590" s="3"/>
+      <c r="J2590" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2590" s="3"/>
+      <c r="L2590" s="3"/>
+      <c r="M2590" s="3"/>
+    </row>
+    <row r="2591" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2591" s="3" t="s">
+        <v>3165</v>
+      </c>
+      <c r="B2591" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2591" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2591" s="3">
+        <v>5596729842</v>
+      </c>
+      <c r="E2591" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2591" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2591" s="3"/>
+      <c r="H2591" s="3"/>
+      <c r="I2591" s="3"/>
+      <c r="J2591" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2591" s="3"/>
+      <c r="L2591" s="3"/>
+      <c r="M2591" s="3"/>
+    </row>
+    <row r="2592" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2592" s="3" t="s">
+        <v>3166</v>
+      </c>
+      <c r="B2592" s="3"/>
+      <c r="C2592" s="3"/>
+      <c r="D2592" s="3">
+        <v>5596878983</v>
+      </c>
+      <c r="E2592" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2592" s="3" t="s">
+        <v>3167</v>
+      </c>
+      <c r="G2592" s="3"/>
+      <c r="H2592" s="3"/>
+      <c r="I2592" s="3"/>
+      <c r="J2592" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2592" s="3"/>
+      <c r="L2592" s="3"/>
+      <c r="M2592" s="3"/>
+    </row>
+    <row r="2593" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2593" s="3" t="s">
+        <v>3168</v>
+      </c>
+      <c r="B2593" s="3"/>
+      <c r="C2593" s="3"/>
+      <c r="D2593" s="3">
+        <v>5596917082</v>
+      </c>
+      <c r="E2593" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2593" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="G2593" s="3"/>
+      <c r="H2593" s="3"/>
+      <c r="I2593" s="3"/>
+      <c r="J2593" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2593" s="3"/>
+      <c r="L2593" s="3"/>
+      <c r="M2593" s="3"/>
+    </row>
+    <row r="2594" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2594" s="3" t="s">
+        <v>3169</v>
+      </c>
+      <c r="B2594" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2594" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2594" s="3">
+        <v>5597064539</v>
+      </c>
+      <c r="E2594" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2594" s="3" t="s">
+        <v>3170</v>
+      </c>
+      <c r="G2594" s="3"/>
+      <c r="H2594" s="3"/>
+      <c r="I2594" s="3"/>
+      <c r="J2594" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2594" s="3"/>
+      <c r="L2594" s="3"/>
+      <c r="M2594" s="3"/>
+    </row>
+    <row r="2595" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2595" s="3" t="s">
+        <v>3171</v>
+      </c>
+      <c r="B2595" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2595" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2595" s="3">
+        <v>5597049327</v>
+      </c>
+      <c r="E2595" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2595" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2595" s="3"/>
+      <c r="H2595" s="3"/>
+      <c r="I2595" s="3"/>
+      <c r="J2595" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2595" s="3"/>
+      <c r="L2595" s="3"/>
+      <c r="M2595" s="3"/>
+    </row>
+    <row r="2596" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2596" s="3" t="s">
+        <v>3172</v>
+      </c>
+      <c r="B2596" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2596" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2596" s="3">
+        <v>5597072086</v>
+      </c>
+      <c r="E2596" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2596" s="3" t="s">
+        <v>2782</v>
+      </c>
+      <c r="G2596" s="3"/>
+      <c r="H2596" s="3"/>
+      <c r="I2596" s="3"/>
+      <c r="J2596" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2596" s="3"/>
+      <c r="L2596" s="3"/>
+      <c r="M2596" s="3"/>
+    </row>
+    <row r="2597" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2597" s="3" t="s">
+        <v>3173</v>
+      </c>
+      <c r="B2597" s="3"/>
+      <c r="C2597" s="3"/>
+      <c r="D2597" s="3">
+        <v>5597073734</v>
+      </c>
+      <c r="E2597" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2597" s="3" t="s">
+        <v>2293</v>
+      </c>
+      <c r="G2597" s="3"/>
+      <c r="H2597" s="3"/>
+      <c r="I2597" s="3"/>
+      <c r="J2597" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2597" s="3"/>
+      <c r="L2597" s="3"/>
+      <c r="M2597" s="3"/>
+    </row>
+    <row r="2598" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2598" s="3" t="s">
+        <v>3173</v>
+      </c>
+      <c r="B2598" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2598" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2598" s="3">
+        <v>5597081350</v>
+      </c>
+      <c r="E2598" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2598" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2598" s="3"/>
+      <c r="H2598" s="3"/>
+      <c r="I2598" s="3"/>
+      <c r="J2598" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2598" s="3"/>
+      <c r="L2598" s="3"/>
+      <c r="M2598" s="3"/>
+    </row>
+    <row r="2599" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2599" s="3" t="s">
+        <v>3174</v>
+      </c>
+      <c r="B2599" s="3"/>
+      <c r="C2599" s="3"/>
+      <c r="D2599" s="3">
+        <v>5597121493</v>
+      </c>
+      <c r="E2599" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2599" s="3" t="s">
+        <v>2293</v>
+      </c>
+      <c r="G2599" s="3"/>
+      <c r="H2599" s="3"/>
+      <c r="I2599" s="3"/>
+      <c r="J2599" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2599" s="3"/>
+      <c r="L2599" s="3"/>
+      <c r="M2599" s="3"/>
+    </row>
+    <row r="2600" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2600" s="3" t="s">
+        <v>3175</v>
+      </c>
+      <c r="B2600" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2600" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2600" s="3">
+        <v>5597330183</v>
+      </c>
+      <c r="E2600" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2600" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="G2600" s="3"/>
+      <c r="H2600" s="3"/>
+      <c r="I2600" s="3"/>
+      <c r="J2600" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2600" s="3"/>
+      <c r="L2600" s="3"/>
+      <c r="M2600" s="3"/>
+    </row>
+    <row r="2601" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2601" s="3" t="s">
+        <v>3176</v>
+      </c>
+      <c r="B2601" s="3"/>
+      <c r="C2601" s="3"/>
+      <c r="D2601" s="3">
+        <v>5597487207</v>
+      </c>
+      <c r="E2601" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2601" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G2601" s="3"/>
+      <c r="H2601" s="3"/>
+      <c r="I2601" s="3"/>
+      <c r="J2601" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2601" s="3"/>
+      <c r="L2601" s="3"/>
+      <c r="M2601" s="3"/>
+    </row>
+    <row r="2602" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2602" s="3" t="s">
+        <v>3177</v>
+      </c>
+      <c r="B2602" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2602" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2602" s="3">
+        <v>5597493898</v>
+      </c>
+      <c r="E2602" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2602" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G2602" s="3"/>
+      <c r="H2602" s="3"/>
+      <c r="I2602" s="3"/>
+      <c r="J2602" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2602" s="3"/>
+      <c r="L2602" s="3"/>
+      <c r="M2602" s="3"/>
+    </row>
+    <row r="2603" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2603" s="3" t="s">
+        <v>3178</v>
+      </c>
+      <c r="B2603" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2603" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2603" s="3">
+        <v>5597627215</v>
+      </c>
+      <c r="E2603" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2603" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="G2603" s="3"/>
+      <c r="H2603" s="3"/>
+      <c r="I2603" s="3"/>
+      <c r="J2603" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2603" s="3"/>
+      <c r="L2603" s="3"/>
+      <c r="M2603" s="3"/>
+    </row>
+    <row r="2604" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2604" s="3" t="s">
+        <v>3179</v>
+      </c>
+      <c r="B2604" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2604" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2604" s="3">
+        <v>5597869101</v>
+      </c>
+      <c r="E2604" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2604" s="3" t="s">
+        <v>2090</v>
+      </c>
+      <c r="G2604" s="3"/>
+      <c r="H2604" s="3"/>
+      <c r="I2604" s="3"/>
+      <c r="J2604" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2604" s="3"/>
+      <c r="L2604" s="3"/>
+      <c r="M2604" s="3"/>
+    </row>
+    <row r="2605" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2605" s="3" t="s">
+        <v>3180</v>
+      </c>
+      <c r="B2605" s="3"/>
+      <c r="C2605" s="3"/>
+      <c r="D2605" s="3">
+        <v>5597980654</v>
+      </c>
+      <c r="E2605" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2605" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2605" s="3"/>
+      <c r="H2605" s="3"/>
+      <c r="I2605" s="3"/>
+      <c r="J2605" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2605" s="3"/>
+      <c r="L2605" s="3"/>
+      <c r="M2605" s="3"/>
+    </row>
+    <row r="2606" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2606" s="3" t="s">
+        <v>3181</v>
+      </c>
+      <c r="B2606" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2606" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2606" s="3">
+        <v>5598182468</v>
+      </c>
+      <c r="E2606" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2606" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="G2606" s="3"/>
+      <c r="H2606" s="3"/>
+      <c r="I2606" s="3"/>
+      <c r="J2606" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2606" s="3"/>
+      <c r="L2606" s="3"/>
+      <c r="M2606" s="3"/>
+    </row>
+    <row r="2607" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2607" s="3" t="s">
+        <v>3182</v>
+      </c>
+      <c r="B2607" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2607" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2607" s="3">
+        <v>5598469850</v>
+      </c>
+      <c r="E2607" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2607" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G2607" s="3"/>
+      <c r="H2607" s="3"/>
+      <c r="I2607" s="3"/>
+      <c r="J2607" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2607" s="3"/>
+      <c r="L2607" s="3"/>
+      <c r="M2607" s="3"/>
+    </row>
+    <row r="2608" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2608" s="3" t="s">
+        <v>3183</v>
+      </c>
+      <c r="B2608" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C2608" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2608" s="3">
+        <v>5598593324</v>
+      </c>
+      <c r="E2608" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2608" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2608" s="3"/>
+      <c r="H2608" s="3"/>
+      <c r="I2608" s="3"/>
+      <c r="J2608" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2608" s="3"/>
+      <c r="L2608" s="3"/>
+      <c r="M2608" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
